--- a/research/traditional_assets/database/data/panama/panama_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/panama/panama_hotel_gaming.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1001427133900049</v>
+        <v>0.09992610660652988</v>
       </c>
       <c r="C2">
-        <v>13.75343429661672</v>
+        <v>13.62774406877363</v>
       </c>
       <c r="D2">
-        <v>11.13343429661673</v>
+        <v>11.14514406877363</v>
       </c>
       <c r="E2">
-        <v>-11.8</v>
+        <v>-11.6626</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1374</v>
       </c>
       <c r="G2">
         <v>2.62</v>
@@ -1439,28 +1439,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006911219999999999</v>
       </c>
       <c r="N2">
-        <v>3.789183673469388</v>
+        <v>3.782272453469388</v>
       </c>
       <c r="O2">
-        <v>0.9472959183673471</v>
+        <v>0.945568113367347</v>
       </c>
       <c r="P2">
-        <v>2.841887755102041</v>
+        <v>2.836704340102041</v>
       </c>
       <c r="Q2">
-        <v>4.011887755102041</v>
+        <v>4.006704340102041</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1001427133900049</v>
+        <v>0.1005544006126565</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815167</v>
+        <v>0.7537149342624373</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>548.265526704314</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09992610660652988</v>
+        <v>0.09970949982305488</v>
       </c>
       <c r="C3">
-        <v>13.62774406877363</v>
+        <v>13.50207849875471</v>
       </c>
       <c r="D3">
-        <v>11.14514406877363</v>
+        <v>11.15687849875471</v>
       </c>
       <c r="E3">
-        <v>-11.6626</v>
+        <v>-11.5252</v>
       </c>
       <c r="F3">
-        <v>0.1374</v>
+        <v>0.2748</v>
       </c>
       <c r="G3">
         <v>2.62</v>
@@ -1521,28 +1521,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M3">
-        <v>0.006911219999999999</v>
+        <v>0.01382244</v>
       </c>
       <c r="N3">
-        <v>3.782272453469388</v>
+        <v>3.775361233469388</v>
       </c>
       <c r="O3">
-        <v>0.945568113367347</v>
+        <v>0.943840308367347</v>
       </c>
       <c r="P3">
-        <v>2.836704340102041</v>
+        <v>2.831520925102041</v>
       </c>
       <c r="Q3">
-        <v>4.006704340102041</v>
+        <v>4.00152092510204</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1005544006126565</v>
+        <v>0.1009744896153621</v>
       </c>
       <c r="T3">
-        <v>0.7537149342624373</v>
+        <v>0.7594976175082747</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>548.265526704314</v>
+        <v>274.132763352157</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09970949982305488</v>
+        <v>0.09949289303957985</v>
       </c>
       <c r="C4">
-        <v>13.50207849875471</v>
+        <v>13.3764376645268</v>
       </c>
       <c r="D4">
-        <v>11.15687849875471</v>
+        <v>11.1686376645268</v>
       </c>
       <c r="E4">
-        <v>-11.5252</v>
+        <v>-11.3878</v>
       </c>
       <c r="F4">
-        <v>0.2748</v>
+        <v>0.4122</v>
       </c>
       <c r="G4">
         <v>2.62</v>
@@ -1603,28 +1603,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M4">
-        <v>0.01382244</v>
+        <v>0.02073366</v>
       </c>
       <c r="N4">
-        <v>3.775361233469388</v>
+        <v>3.768450013469388</v>
       </c>
       <c r="O4">
-        <v>0.943840308367347</v>
+        <v>0.9421125033673471</v>
       </c>
       <c r="P4">
-        <v>2.831520925102041</v>
+        <v>2.826337510102041</v>
       </c>
       <c r="Q4">
-        <v>4.00152092510204</v>
+        <v>3.996337510102041</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1009744896153621</v>
+        <v>0.1014032402469895</v>
       </c>
       <c r="T4">
-        <v>0.7594976175082747</v>
+        <v>0.7653995313365003</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>274.132763352157</v>
+        <v>182.7551755681046</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09949289303957985</v>
+        <v>0.09927628625610485</v>
       </c>
       <c r="C5">
-        <v>13.3764376645268</v>
+        <v>13.25082164438576</v>
       </c>
       <c r="D5">
-        <v>11.1686376645268</v>
+        <v>11.18042164438576</v>
       </c>
       <c r="E5">
-        <v>-11.3878</v>
+        <v>-11.2504</v>
       </c>
       <c r="F5">
-        <v>0.4122</v>
+        <v>0.5496</v>
       </c>
       <c r="G5">
         <v>2.62</v>
@@ -1685,28 +1685,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M5">
-        <v>0.02073366</v>
+        <v>0.02764488</v>
       </c>
       <c r="N5">
-        <v>3.768450013469388</v>
+        <v>3.761538793469388</v>
       </c>
       <c r="O5">
-        <v>0.9421125033673471</v>
+        <v>0.9403846983673471</v>
       </c>
       <c r="P5">
-        <v>2.826337510102041</v>
+        <v>2.821154095102041</v>
       </c>
       <c r="Q5">
-        <v>3.996337510102041</v>
+        <v>3.991154095102041</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1014032402469895</v>
+        <v>0.1018409231834426</v>
       </c>
       <c r="T5">
-        <v>0.7653995313365003</v>
+        <v>0.7714244017028141</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>182.7551755681046</v>
+        <v>137.0663816760785</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09927628625610485</v>
+        <v>0.09905967947262984</v>
       </c>
       <c r="C6">
-        <v>13.25082164438576</v>
+        <v>13.12523051695824</v>
       </c>
       <c r="D6">
-        <v>11.18042164438576</v>
+        <v>11.19223051695824</v>
       </c>
       <c r="E6">
-        <v>-11.2504</v>
+        <v>-11.113</v>
       </c>
       <c r="F6">
-        <v>0.5496</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G6">
         <v>2.62</v>
@@ -1767,28 +1767,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M6">
-        <v>0.02764488</v>
+        <v>0.0345561</v>
       </c>
       <c r="N6">
-        <v>3.761538793469388</v>
+        <v>3.754627573469388</v>
       </c>
       <c r="O6">
-        <v>0.9403846983673471</v>
+        <v>0.938656893367347</v>
       </c>
       <c r="P6">
-        <v>2.821154095102041</v>
+        <v>2.815970680102041</v>
       </c>
       <c r="Q6">
-        <v>3.991154095102041</v>
+        <v>3.985970680102041</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1018409231834426</v>
+        <v>0.1022878204975051</v>
       </c>
       <c r="T6">
-        <v>0.7714244017028141</v>
+        <v>0.7775761114452608</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>137.0663816760785</v>
+        <v>109.6531053408628</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09905967947262984</v>
+        <v>0.09884307268915482</v>
       </c>
       <c r="C7">
-        <v>13.12523051695824</v>
+        <v>12.99966436120344</v>
       </c>
       <c r="D7">
-        <v>11.19223051695824</v>
+        <v>11.20406436120344</v>
       </c>
       <c r="E7">
-        <v>-11.113</v>
+        <v>-10.9756</v>
       </c>
       <c r="F7">
-        <v>0.6870000000000001</v>
+        <v>0.8244000000000001</v>
       </c>
       <c r="G7">
         <v>2.62</v>
@@ -1849,28 +1849,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M7">
-        <v>0.0345561</v>
+        <v>0.04146732</v>
       </c>
       <c r="N7">
-        <v>3.754627573469388</v>
+        <v>3.747716353469388</v>
       </c>
       <c r="O7">
-        <v>0.938656893367347</v>
+        <v>0.936929088367347</v>
       </c>
       <c r="P7">
-        <v>2.815970680102041</v>
+        <v>2.810787265102041</v>
       </c>
       <c r="Q7">
-        <v>3.985970680102041</v>
+        <v>3.980787265102041</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1022878204975051</v>
+        <v>0.1027442262650583</v>
       </c>
       <c r="T7">
-        <v>0.7775761114452608</v>
+        <v>0.7838587086290362</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>109.6531053408628</v>
+        <v>91.37758778405231</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09884307268915482</v>
+        <v>0.09862646590567982</v>
       </c>
       <c r="C8">
-        <v>12.99966436120344</v>
+        <v>12.87412325641485</v>
       </c>
       <c r="D8">
-        <v>11.20406436120344</v>
+        <v>11.21592325641485</v>
       </c>
       <c r="E8">
-        <v>-10.9756</v>
+        <v>-10.8382</v>
       </c>
       <c r="F8">
-        <v>0.8244</v>
+        <v>0.9617999999999999</v>
       </c>
       <c r="G8">
         <v>2.62</v>
@@ -1931,28 +1931,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M8">
-        <v>0.04146732</v>
+        <v>0.04837853999999999</v>
       </c>
       <c r="N8">
-        <v>3.747716353469388</v>
+        <v>3.740805133469388</v>
       </c>
       <c r="O8">
-        <v>0.936929088367347</v>
+        <v>0.9352012833673471</v>
       </c>
       <c r="P8">
-        <v>2.810787265102041</v>
+        <v>2.805603850102041</v>
       </c>
       <c r="Q8">
-        <v>3.980787265102041</v>
+        <v>3.975603850102041</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1027442262650583</v>
+        <v>0.1032104472104084</v>
       </c>
       <c r="T8">
-        <v>0.7838587086290362</v>
+        <v>0.7902764154296669</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>91.37758778405231</v>
+        <v>78.32364667204486</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09862646590567981</v>
+        <v>0.09840985912220482</v>
       </c>
       <c r="C9">
-        <v>12.87412325641486</v>
+        <v>12.74860728222203</v>
       </c>
       <c r="D9">
-        <v>11.21592325641486</v>
+        <v>11.22780728222203</v>
       </c>
       <c r="E9">
-        <v>-10.8382</v>
+        <v>-10.7008</v>
       </c>
       <c r="F9">
-        <v>0.9618000000000001</v>
+        <v>1.0992</v>
       </c>
       <c r="G9">
         <v>2.62</v>
@@ -2013,28 +2013,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M9">
-        <v>0.04837854</v>
+        <v>0.05528975999999999</v>
       </c>
       <c r="N9">
-        <v>3.740805133469388</v>
+        <v>3.733893913469388</v>
       </c>
       <c r="O9">
-        <v>0.9352012833673471</v>
+        <v>0.9334734783673471</v>
       </c>
       <c r="P9">
-        <v>2.805603850102041</v>
+        <v>2.800420435102041</v>
       </c>
       <c r="Q9">
-        <v>3.975603850102041</v>
+        <v>3.970420435102041</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1032104472104084</v>
+        <v>0.1036868033937009</v>
       </c>
       <c r="T9">
-        <v>0.7902764154296669</v>
+        <v>0.7968336375955287</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>78.32364667204483</v>
+        <v>68.53319083803925</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09840985912220482</v>
+        <v>0.0981932523387298</v>
       </c>
       <c r="C10">
-        <v>12.74860728222203</v>
+        <v>12.62311651859238</v>
       </c>
       <c r="D10">
-        <v>11.22780728222203</v>
+        <v>11.23971651859237</v>
       </c>
       <c r="E10">
-        <v>-10.7008</v>
+        <v>-10.5634</v>
       </c>
       <c r="F10">
-        <v>1.0992</v>
+        <v>1.2366</v>
       </c>
       <c r="G10">
         <v>2.62</v>
@@ -2095,28 +2095,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M10">
-        <v>0.05528975999999999</v>
+        <v>0.06220098</v>
       </c>
       <c r="N10">
-        <v>3.733893913469388</v>
+        <v>3.726982693469388</v>
       </c>
       <c r="O10">
-        <v>0.9334734783673471</v>
+        <v>0.931745673367347</v>
       </c>
       <c r="P10">
-        <v>2.800420435102041</v>
+        <v>2.795237020102041</v>
       </c>
       <c r="Q10">
-        <v>3.970420435102041</v>
+        <v>3.965237020102041</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1036868033937009</v>
+        <v>0.1041736289436591</v>
       </c>
       <c r="T10">
-        <v>0.7968336375955287</v>
+        <v>0.8035349745342666</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>68.53319083803925</v>
+        <v>60.91839185603488</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0981932523387298</v>
+        <v>0.09797664555525477</v>
       </c>
       <c r="C11">
-        <v>12.62311651859238</v>
+        <v>12.49765104583294</v>
       </c>
       <c r="D11">
-        <v>11.23971651859237</v>
+        <v>11.25165104583294</v>
       </c>
       <c r="E11">
-        <v>-10.5634</v>
+        <v>-10.426</v>
       </c>
       <c r="F11">
-        <v>1.2366</v>
+        <v>1.374</v>
       </c>
       <c r="G11">
         <v>2.62</v>
@@ -2177,28 +2177,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M11">
-        <v>0.06220098</v>
+        <v>0.06911219999999998</v>
       </c>
       <c r="N11">
-        <v>3.726982693469388</v>
+        <v>3.720071473469388</v>
       </c>
       <c r="O11">
-        <v>0.931745673367347</v>
+        <v>0.930017868367347</v>
       </c>
       <c r="P11">
-        <v>2.795237020102041</v>
+        <v>2.790053605102041</v>
       </c>
       <c r="Q11">
-        <v>3.965237020102041</v>
+        <v>3.960053605102041</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1041736289436591</v>
+        <v>0.104671272839172</v>
       </c>
       <c r="T11">
-        <v>0.8035349745342666</v>
+        <v>0.8103852300716431</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>60.91839185603488</v>
+        <v>54.8265526704314</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09797664555525477</v>
+        <v>0.09776003877177977</v>
       </c>
       <c r="C12">
-        <v>12.49765104583294</v>
+        <v>12.37221094459221</v>
       </c>
       <c r="D12">
-        <v>11.25165104583294</v>
+        <v>11.26361094459221</v>
       </c>
       <c r="E12">
-        <v>-10.426</v>
+        <v>-10.2886</v>
       </c>
       <c r="F12">
-        <v>1.374</v>
+        <v>1.5114</v>
       </c>
       <c r="G12">
         <v>2.62</v>
@@ -2259,28 +2259,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M12">
-        <v>0.0691122</v>
+        <v>0.07602341999999999</v>
       </c>
       <c r="N12">
-        <v>3.720071473469388</v>
+        <v>3.713160253469388</v>
       </c>
       <c r="O12">
-        <v>0.930017868367347</v>
+        <v>0.9282900633673471</v>
       </c>
       <c r="P12">
-        <v>2.790053605102041</v>
+        <v>2.784870190102041</v>
       </c>
       <c r="Q12">
-        <v>3.960053605102041</v>
+        <v>3.954870190102041</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.104671272839172</v>
+        <v>0.1051800997435728</v>
       </c>
       <c r="T12">
-        <v>0.8103852300716431</v>
+        <v>0.8173894239357024</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>54.82655267043139</v>
+        <v>49.84232060948309</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09776003877177977</v>
+        <v>0.09754343198830476</v>
       </c>
       <c r="C13">
-        <v>12.37221094459221</v>
+        <v>12.24679629586196</v>
       </c>
       <c r="D13">
-        <v>11.26361094459221</v>
+        <v>11.27559629586196</v>
       </c>
       <c r="E13">
-        <v>-10.2886</v>
+        <v>-10.1512</v>
       </c>
       <c r="F13">
-        <v>1.5114</v>
+        <v>1.6488</v>
       </c>
       <c r="G13">
         <v>2.62</v>
@@ -2341,28 +2341,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M13">
-        <v>0.07602341999999999</v>
+        <v>0.08293464</v>
       </c>
       <c r="N13">
-        <v>3.713160253469388</v>
+        <v>3.706249033469388</v>
       </c>
       <c r="O13">
-        <v>0.9282900633673471</v>
+        <v>0.9265622583673471</v>
       </c>
       <c r="P13">
-        <v>2.784870190102041</v>
+        <v>2.779686775102041</v>
       </c>
       <c r="Q13">
-        <v>3.954870190102041</v>
+        <v>3.949686775102041</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1051800997435728</v>
+        <v>0.1057004908958009</v>
       </c>
       <c r="T13">
-        <v>0.8173894239357024</v>
+        <v>0.8245528040239446</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>49.84232060948309</v>
+        <v>45.68879389202615</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09754343198830476</v>
+        <v>0.09732682520482974</v>
       </c>
       <c r="C14">
-        <v>12.24679629586196</v>
+        <v>12.12140718097904</v>
       </c>
       <c r="D14">
-        <v>11.27559629586196</v>
+        <v>11.28760718097905</v>
       </c>
       <c r="E14">
-        <v>-10.1512</v>
+        <v>-10.0138</v>
       </c>
       <c r="F14">
-        <v>1.6488</v>
+        <v>1.7862</v>
       </c>
       <c r="G14">
         <v>2.62</v>
@@ -2423,28 +2423,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M14">
-        <v>0.08293464</v>
+        <v>0.08984586</v>
       </c>
       <c r="N14">
-        <v>3.706249033469388</v>
+        <v>3.699337813469388</v>
       </c>
       <c r="O14">
-        <v>0.9265622583673471</v>
+        <v>0.924834453367347</v>
       </c>
       <c r="P14">
-        <v>2.779686775102041</v>
+        <v>2.774503360102041</v>
       </c>
       <c r="Q14">
-        <v>3.949686775102041</v>
+        <v>3.944503360102041</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1057004908958009</v>
+        <v>0.1062328450630227</v>
       </c>
       <c r="T14">
-        <v>0.8245528040239446</v>
+        <v>0.8318808595165142</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>45.68879389202615</v>
+        <v>42.17427128494722</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09732682520482974</v>
+        <v>0.09711021842135473</v>
       </c>
       <c r="C15">
-        <v>12.12140718097904</v>
+        <v>11.99604368162725</v>
       </c>
       <c r="D15">
-        <v>11.28760718097905</v>
+        <v>11.29964368162725</v>
       </c>
       <c r="E15">
-        <v>-10.0138</v>
+        <v>-9.8764</v>
       </c>
       <c r="F15">
-        <v>1.7862</v>
+        <v>1.9236</v>
       </c>
       <c r="G15">
         <v>2.62</v>
@@ -2505,28 +2505,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M15">
-        <v>0.08984586</v>
+        <v>0.09675708000000001</v>
       </c>
       <c r="N15">
-        <v>3.699337813469388</v>
+        <v>3.692426593469388</v>
       </c>
       <c r="O15">
-        <v>0.924834453367347</v>
+        <v>0.923106648367347</v>
       </c>
       <c r="P15">
-        <v>2.774503360102041</v>
+        <v>2.769319945102041</v>
       </c>
       <c r="Q15">
-        <v>3.944503360102041</v>
+        <v>3.939319945102041</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1062328450630227</v>
+        <v>0.1067775795597148</v>
       </c>
       <c r="T15">
-        <v>0.8318808595165142</v>
+        <v>0.8393793349042601</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>42.17427128494722</v>
+        <v>39.16182333602242</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09711021842135473</v>
+        <v>0.09689361163787973</v>
       </c>
       <c r="C16">
-        <v>11.99604368162725</v>
+        <v>11.87070587983914</v>
       </c>
       <c r="D16">
-        <v>11.29964368162725</v>
+        <v>11.31170587983914</v>
       </c>
       <c r="E16">
-        <v>-9.8764</v>
+        <v>-9.739000000000001</v>
       </c>
       <c r="F16">
-        <v>1.9236</v>
+        <v>2.061</v>
       </c>
       <c r="G16">
         <v>2.62</v>
@@ -2587,28 +2587,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M16">
-        <v>0.09675708000000001</v>
+        <v>0.1036683</v>
       </c>
       <c r="N16">
-        <v>3.692426593469388</v>
+        <v>3.685515373469388</v>
       </c>
       <c r="O16">
-        <v>0.923106648367347</v>
+        <v>0.9213788433673471</v>
       </c>
       <c r="P16">
-        <v>2.769319945102041</v>
+        <v>2.764136530102041</v>
       </c>
       <c r="Q16">
-        <v>3.939319945102041</v>
+        <v>3.934136530102041</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1067775795597148</v>
+        <v>0.107335131338682</v>
       </c>
       <c r="T16">
-        <v>0.8393793349042601</v>
+        <v>0.8470542450070115</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>39.16182333602242</v>
+        <v>36.55103511362092</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09689361163787973</v>
+        <v>0.0966770048544047</v>
       </c>
       <c r="C17">
-        <v>11.87070587983914</v>
+        <v>11.74539385799794</v>
       </c>
       <c r="D17">
-        <v>11.31170587983914</v>
+        <v>11.32379385799794</v>
       </c>
       <c r="E17">
-        <v>-9.739000000000001</v>
+        <v>-9.601600000000001</v>
       </c>
       <c r="F17">
-        <v>2.061</v>
+        <v>2.1984</v>
       </c>
       <c r="G17">
         <v>2.62</v>
@@ -2669,28 +2669,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M17">
-        <v>0.1036683</v>
+        <v>0.11057952</v>
       </c>
       <c r="N17">
-        <v>3.685515373469388</v>
+        <v>3.678604153469388</v>
       </c>
       <c r="O17">
-        <v>0.9213788433673471</v>
+        <v>0.9196510383673471</v>
       </c>
       <c r="P17">
-        <v>2.764136530102041</v>
+        <v>2.758953115102041</v>
       </c>
       <c r="Q17">
-        <v>3.934136530102041</v>
+        <v>3.928953115102041</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.107335131338682</v>
+        <v>0.1079059581600056</v>
       </c>
       <c r="T17">
-        <v>0.8470542450070115</v>
+        <v>0.8549118910645905</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>36.55103511362093</v>
+        <v>34.26659541901962</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0966770048544047</v>
+        <v>0.09646039807092968</v>
       </c>
       <c r="C18">
-        <v>11.74539385799794</v>
+        <v>11.6201076988394</v>
       </c>
       <c r="D18">
-        <v>11.32379385799794</v>
+        <v>11.3359076988394</v>
       </c>
       <c r="E18">
-        <v>-9.601600000000001</v>
+        <v>-9.4642</v>
       </c>
       <c r="F18">
-        <v>2.1984</v>
+        <v>2.3358</v>
       </c>
       <c r="G18">
         <v>2.62</v>
@@ -2751,28 +2751,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M18">
-        <v>0.11057952</v>
+        <v>0.11749074</v>
       </c>
       <c r="N18">
-        <v>3.678604153469388</v>
+        <v>3.671692933469388</v>
       </c>
       <c r="O18">
-        <v>0.9196510383673471</v>
+        <v>0.917923233367347</v>
       </c>
       <c r="P18">
-        <v>2.758953115102041</v>
+        <v>2.753769700102041</v>
       </c>
       <c r="Q18">
-        <v>3.928953115102041</v>
+        <v>3.923769700102041</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1079059581600056</v>
+        <v>0.1084905398444936</v>
       </c>
       <c r="T18">
-        <v>0.8549118910645905</v>
+        <v>0.8629588779910269</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>34.26659541901962</v>
+        <v>32.25091333554787</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09646039807092968</v>
+        <v>0.09624379128745469</v>
       </c>
       <c r="C19">
-        <v>11.6201076988394</v>
+        <v>11.49484748545367</v>
       </c>
       <c r="D19">
-        <v>11.3359076988394</v>
+        <v>11.34804748545367</v>
       </c>
       <c r="E19">
-        <v>-9.4642</v>
+        <v>-9.3268</v>
       </c>
       <c r="F19">
-        <v>2.3358</v>
+        <v>2.4732</v>
       </c>
       <c r="G19">
         <v>2.62</v>
@@ -2833,28 +2833,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M19">
-        <v>0.11749074</v>
+        <v>0.12440196</v>
       </c>
       <c r="N19">
-        <v>3.671692933469388</v>
+        <v>3.664781713469388</v>
       </c>
       <c r="O19">
-        <v>0.917923233367347</v>
+        <v>0.916195428367347</v>
       </c>
       <c r="P19">
-        <v>2.753769700102041</v>
+        <v>2.748586285102041</v>
       </c>
       <c r="Q19">
-        <v>3.923769700102041</v>
+        <v>3.918586285102041</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1084905398444936</v>
+        <v>0.1090893796188472</v>
       </c>
       <c r="T19">
-        <v>0.8629588779910269</v>
+        <v>0.8712021328912786</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>32.25091333554787</v>
+        <v>30.45919592801744</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09624379128745469</v>
+        <v>0.09602718450397969</v>
       </c>
       <c r="C20">
-        <v>11.49484748545367</v>
+        <v>11.36961330128723</v>
       </c>
       <c r="D20">
-        <v>11.34804748545367</v>
+        <v>11.36021330128723</v>
       </c>
       <c r="E20">
-        <v>-9.3268</v>
+        <v>-9.189400000000001</v>
       </c>
       <c r="F20">
-        <v>2.4732</v>
+        <v>2.6106</v>
       </c>
       <c r="G20">
         <v>2.62</v>
@@ -2915,28 +2915,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M20">
-        <v>0.12440196</v>
+        <v>0.13131318</v>
       </c>
       <c r="N20">
-        <v>3.664781713469388</v>
+        <v>3.657870493469388</v>
       </c>
       <c r="O20">
-        <v>0.916195428367347</v>
+        <v>0.9144676233673471</v>
       </c>
       <c r="P20">
-        <v>2.748586285102041</v>
+        <v>2.743402870102041</v>
       </c>
       <c r="Q20">
-        <v>3.918586285102041</v>
+        <v>3.913402870102041</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1090893796188472</v>
+        <v>0.1097030055604687</v>
       </c>
       <c r="T20">
-        <v>0.8712021328912786</v>
+        <v>0.8796489249495614</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>30.45919592801744</v>
+        <v>28.85608035285863</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09602718450397969</v>
+        <v>0.09581057772050465</v>
       </c>
       <c r="C21">
-        <v>11.36961330128723</v>
+        <v>11.24440523014475</v>
       </c>
       <c r="D21">
-        <v>11.36021330128723</v>
+        <v>11.37240523014475</v>
       </c>
       <c r="E21">
-        <v>-9.189400000000001</v>
+        <v>-9.052</v>
       </c>
       <c r="F21">
-        <v>2.6106</v>
+        <v>2.748</v>
       </c>
       <c r="G21">
         <v>2.62</v>
@@ -2997,28 +2997,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M21">
-        <v>0.13131318</v>
+        <v>0.1382244</v>
       </c>
       <c r="N21">
-        <v>3.657870493469388</v>
+        <v>3.650959273469388</v>
       </c>
       <c r="O21">
-        <v>0.9144676233673471</v>
+        <v>0.9127398183673471</v>
       </c>
       <c r="P21">
-        <v>2.743402870102041</v>
+        <v>2.738219455102041</v>
       </c>
       <c r="Q21">
-        <v>3.913402870102041</v>
+        <v>3.908219455102041</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1097030055604687</v>
+        <v>0.1103319721506308</v>
       </c>
       <c r="T21">
-        <v>0.8796489249495614</v>
+        <v>0.8883068868093011</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>28.85608035285863</v>
+        <v>27.41327633521569</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09581057772050465</v>
+        <v>0.09559397093702966</v>
       </c>
       <c r="C22">
-        <v>11.24440523014475</v>
+        <v>11.11922335619109</v>
       </c>
       <c r="D22">
-        <v>11.37240523014475</v>
+        <v>11.38462335619109</v>
       </c>
       <c r="E22">
-        <v>-9.052</v>
+        <v>-8.9146</v>
       </c>
       <c r="F22">
-        <v>2.748</v>
+        <v>2.8854</v>
       </c>
       <c r="G22">
         <v>2.62</v>
@@ -3079,28 +3079,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M22">
-        <v>0.1382244</v>
+        <v>0.14513562</v>
       </c>
       <c r="N22">
-        <v>3.650959273469388</v>
+        <v>3.644048053469388</v>
       </c>
       <c r="O22">
-        <v>0.9127398183673471</v>
+        <v>0.9110120133673471</v>
       </c>
       <c r="P22">
-        <v>2.738219455102041</v>
+        <v>2.733036040102041</v>
       </c>
       <c r="Q22">
-        <v>3.908219455102041</v>
+        <v>3.903036040102041</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1103319721506308</v>
+        <v>0.1109768619456072</v>
       </c>
       <c r="T22">
-        <v>0.8883068868093011</v>
+        <v>0.8971840375768824</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>27.41327633521569</v>
+        <v>26.10788222401495</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09559397093702965</v>
+        <v>0.09537736415355463</v>
       </c>
       <c r="C23">
-        <v>11.11922335619109</v>
+        <v>10.99406776395317</v>
       </c>
       <c r="D23">
-        <v>11.38462335619109</v>
+        <v>11.39686776395317</v>
       </c>
       <c r="E23">
-        <v>-8.9146</v>
+        <v>-8.777200000000001</v>
       </c>
       <c r="F23">
-        <v>2.8854</v>
+        <v>3.0228</v>
       </c>
       <c r="G23">
         <v>2.62</v>
@@ -3161,28 +3161,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M23">
-        <v>0.14513562</v>
+        <v>0.15204684</v>
       </c>
       <c r="N23">
-        <v>3.644048053469388</v>
+        <v>3.637136833469388</v>
       </c>
       <c r="O23">
-        <v>0.9110120133673471</v>
+        <v>0.909284208367347</v>
       </c>
       <c r="P23">
-        <v>2.733036040102041</v>
+        <v>2.727852625102041</v>
       </c>
       <c r="Q23">
-        <v>3.903036040102041</v>
+        <v>3.897852625102041</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1109768619456072</v>
+        <v>0.1116382873763521</v>
       </c>
       <c r="T23">
-        <v>0.8971840375768824</v>
+        <v>0.9062888075949144</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>26.10788222401495</v>
+        <v>24.92116030474154</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09537736415355463</v>
+        <v>0.09516075737007963</v>
       </c>
       <c r="C24">
-        <v>10.99406776395317</v>
+        <v>10.86893853832193</v>
       </c>
       <c r="D24">
-        <v>11.39686776395317</v>
+        <v>11.40913853832193</v>
       </c>
       <c r="E24">
-        <v>-8.777200000000001</v>
+        <v>-8.639800000000001</v>
       </c>
       <c r="F24">
-        <v>3.0228</v>
+        <v>3.1602</v>
       </c>
       <c r="G24">
         <v>2.62</v>
@@ -3243,28 +3243,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M24">
-        <v>0.15204684</v>
+        <v>0.15895806</v>
       </c>
       <c r="N24">
-        <v>3.637136833469388</v>
+        <v>3.630225613469388</v>
       </c>
       <c r="O24">
-        <v>0.909284208367347</v>
+        <v>0.9075564033673471</v>
       </c>
       <c r="P24">
-        <v>2.727852625102041</v>
+        <v>2.722669210102041</v>
       </c>
       <c r="Q24">
-        <v>3.897852625102041</v>
+        <v>3.892669210102041</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1116382873763521</v>
+        <v>0.1123168926884151</v>
       </c>
       <c r="T24">
-        <v>0.9062888075949144</v>
+        <v>0.9156300651458825</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>24.92116030474154</v>
+        <v>23.83763159583974</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09516075737007963</v>
+        <v>0.0949441505866046</v>
       </c>
       <c r="C25">
-        <v>10.86893853832193</v>
+        <v>10.74383576455435</v>
       </c>
       <c r="D25">
-        <v>11.40913853832193</v>
+        <v>11.42143576455435</v>
       </c>
       <c r="E25">
-        <v>-8.639800000000001</v>
+        <v>-8.5024</v>
       </c>
       <c r="F25">
-        <v>3.1602</v>
+        <v>3.297600000000001</v>
       </c>
       <c r="G25">
         <v>2.62</v>
@@ -3325,28 +3325,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M25">
-        <v>0.15895806</v>
+        <v>0.16586928</v>
       </c>
       <c r="N25">
-        <v>3.630225613469388</v>
+        <v>3.623314393469388</v>
       </c>
       <c r="O25">
-        <v>0.9075564033673471</v>
+        <v>0.9058285983673471</v>
       </c>
       <c r="P25">
-        <v>2.722669210102041</v>
+        <v>2.717485795102041</v>
       </c>
       <c r="Q25">
-        <v>3.892669210102041</v>
+        <v>3.887485795102041</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1123168926884151</v>
+        <v>0.1130133560350061</v>
       </c>
       <c r="T25">
-        <v>0.9156300651458825</v>
+        <v>0.9252171452639812</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>23.83763159583974</v>
+        <v>22.84439694601308</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0949441505866046</v>
+        <v>0.09472754380312959</v>
       </c>
       <c r="C26">
-        <v>10.74383576455435</v>
+        <v>10.61875952827532</v>
       </c>
       <c r="D26">
-        <v>11.42143576455435</v>
+        <v>11.43375952827532</v>
       </c>
       <c r="E26">
-        <v>-8.502400000000002</v>
+        <v>-8.365</v>
       </c>
       <c r="F26">
-        <v>3.2976</v>
+        <v>3.435</v>
       </c>
       <c r="G26">
         <v>2.62</v>
@@ -3407,28 +3407,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M26">
-        <v>0.16586928</v>
+        <v>0.1727805</v>
       </c>
       <c r="N26">
-        <v>3.623314393469388</v>
+        <v>3.616403173469388</v>
       </c>
       <c r="O26">
-        <v>0.9058285983673471</v>
+        <v>0.9041007933673471</v>
       </c>
       <c r="P26">
-        <v>2.717485795102041</v>
+        <v>2.712302380102041</v>
       </c>
       <c r="Q26">
-        <v>3.887485795102041</v>
+        <v>3.882302380102041</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1130133560350061</v>
+        <v>0.1137283917375061</v>
       </c>
       <c r="T26">
-        <v>0.9252171452639812</v>
+        <v>0.935059880851896</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>22.84439694601308</v>
+        <v>21.93062106817256</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09472754380312959</v>
+        <v>0.09451093701965459</v>
       </c>
       <c r="C27">
-        <v>10.61875952827532</v>
+        <v>10.49370991547975</v>
       </c>
       <c r="D27">
-        <v>11.43375952827532</v>
+        <v>11.44610991547975</v>
       </c>
       <c r="E27">
-        <v>-8.365</v>
+        <v>-8.227600000000001</v>
       </c>
       <c r="F27">
-        <v>3.435</v>
+        <v>3.5724</v>
       </c>
       <c r="G27">
         <v>2.62</v>
@@ -3489,28 +3489,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M27">
-        <v>0.1727805</v>
+        <v>0.17969172</v>
       </c>
       <c r="N27">
-        <v>3.616403173469388</v>
+        <v>3.609491953469388</v>
       </c>
       <c r="O27">
-        <v>0.9041007933673471</v>
+        <v>0.902372988367347</v>
       </c>
       <c r="P27">
-        <v>2.712302380102041</v>
+        <v>2.707118965102041</v>
       </c>
       <c r="Q27">
-        <v>3.882302380102041</v>
+        <v>3.877118965102041</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1137283917375061</v>
+        <v>0.114462752729263</v>
       </c>
       <c r="T27">
-        <v>0.935059880851896</v>
+        <v>0.9451686363205651</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>21.93062106817256</v>
+        <v>21.08713564247361</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09451093701965459</v>
+        <v>0.09429433023617956</v>
       </c>
       <c r="C28">
-        <v>10.49370991547975</v>
+        <v>10.36868701253446</v>
       </c>
       <c r="D28">
-        <v>11.44610991547975</v>
+        <v>11.45848701253446</v>
       </c>
       <c r="E28">
-        <v>-8.227600000000001</v>
+        <v>-8.090199999999999</v>
       </c>
       <c r="F28">
-        <v>3.5724</v>
+        <v>3.7098</v>
       </c>
       <c r="G28">
         <v>2.62</v>
@@ -3571,28 +3571,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M28">
-        <v>0.17969172</v>
+        <v>0.18660294</v>
       </c>
       <c r="N28">
-        <v>3.609491953469388</v>
+        <v>3.602580733469388</v>
       </c>
       <c r="O28">
-        <v>0.902372988367347</v>
+        <v>0.900645183367347</v>
       </c>
       <c r="P28">
-        <v>2.707118965102041</v>
+        <v>2.701935550102041</v>
       </c>
       <c r="Q28">
-        <v>3.877118965102041</v>
+        <v>3.871935550102041</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.114462752729263</v>
+        <v>0.115217233200246</v>
       </c>
       <c r="T28">
-        <v>0.9451686363205651</v>
+        <v>0.9555543439938553</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>21.08713564247361</v>
+        <v>20.30613061867829</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09429433023617956</v>
+        <v>0.09407772345270456</v>
       </c>
       <c r="C29">
-        <v>10.36868701253446</v>
+        <v>10.24369090618026</v>
       </c>
       <c r="D29">
-        <v>11.45848701253446</v>
+        <v>11.47089090618026</v>
       </c>
       <c r="E29">
-        <v>-8.090199999999999</v>
+        <v>-7.9528</v>
       </c>
       <c r="F29">
-        <v>3.7098</v>
+        <v>3.8472</v>
       </c>
       <c r="G29">
         <v>2.62</v>
@@ -3653,28 +3653,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M29">
-        <v>0.18660294</v>
+        <v>0.19351416</v>
       </c>
       <c r="N29">
-        <v>3.602580733469388</v>
+        <v>3.595669513469388</v>
       </c>
       <c r="O29">
-        <v>0.900645183367347</v>
+        <v>0.8989173783673471</v>
       </c>
       <c r="P29">
-        <v>2.701935550102041</v>
+        <v>2.696752135102041</v>
       </c>
       <c r="Q29">
-        <v>3.871935550102041</v>
+        <v>3.866752135102041</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.115217233200246</v>
+        <v>0.1159926714620897</v>
       </c>
       <c r="T29">
-        <v>0.9555543439938553</v>
+        <v>0.9662285435469592</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>20.30613061867829</v>
+        <v>19.58091166801121</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09407772345270456</v>
+        <v>0.09386111666922954</v>
       </c>
       <c r="C30">
-        <v>10.24369090618026</v>
+        <v>10.11872168353397</v>
       </c>
       <c r="D30">
-        <v>11.47089090618026</v>
+        <v>11.48332168353397</v>
       </c>
       <c r="E30">
-        <v>-7.9528</v>
+        <v>-7.8154</v>
       </c>
       <c r="F30">
-        <v>3.8472</v>
+        <v>3.9846</v>
       </c>
       <c r="G30">
         <v>2.62</v>
@@ -3735,28 +3735,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M30">
-        <v>0.19351416</v>
+        <v>0.20042538</v>
       </c>
       <c r="N30">
-        <v>3.595669513469388</v>
+        <v>3.588758293469388</v>
       </c>
       <c r="O30">
-        <v>0.8989173783673471</v>
+        <v>0.8971895733673471</v>
       </c>
       <c r="P30">
-        <v>2.696752135102041</v>
+        <v>2.691568720102041</v>
       </c>
       <c r="Q30">
-        <v>3.866752135102041</v>
+        <v>3.861568720102041</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1159926714620897</v>
+        <v>0.1167899530552529</v>
       </c>
       <c r="T30">
-        <v>0.9662285435469592</v>
+        <v>0.9772034247776151</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>19.58091166801121</v>
+        <v>18.90570781739013</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09386111666922954</v>
+        <v>0.09364450988575453</v>
       </c>
       <c r="C31">
-        <v>10.11872168353397</v>
+        <v>9.99377943209041</v>
       </c>
       <c r="D31">
-        <v>11.48332168353397</v>
+        <v>11.49577943209041</v>
       </c>
       <c r="E31">
-        <v>-7.8154</v>
+        <v>-7.678000000000001</v>
       </c>
       <c r="F31">
-        <v>3.9846</v>
+        <v>4.122</v>
       </c>
       <c r="G31">
         <v>2.62</v>
@@ -3817,28 +3817,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M31">
-        <v>0.20042538</v>
+        <v>0.2073366</v>
       </c>
       <c r="N31">
-        <v>3.588758293469388</v>
+        <v>3.581847073469388</v>
       </c>
       <c r="O31">
-        <v>0.8971895733673471</v>
+        <v>0.895461768367347</v>
       </c>
       <c r="P31">
-        <v>2.691568720102041</v>
+        <v>2.686385305102041</v>
       </c>
       <c r="Q31">
-        <v>3.861568720102041</v>
+        <v>3.856385305102041</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1167899530552529</v>
+        <v>0.1176100141225065</v>
       </c>
       <c r="T31">
-        <v>0.9772034247776151</v>
+        <v>0.9884918740434327</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>18.90570781739013</v>
+        <v>18.27551755681046</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09364450988575453</v>
+        <v>0.09342790310227952</v>
       </c>
       <c r="C32">
-        <v>9.99377943209041</v>
+        <v>9.868864239724527</v>
       </c>
       <c r="D32">
-        <v>11.49577943209041</v>
+        <v>11.50826423972453</v>
       </c>
       <c r="E32">
-        <v>-7.678000000000001</v>
+        <v>-7.5406</v>
       </c>
       <c r="F32">
-        <v>4.122</v>
+        <v>4.2594</v>
       </c>
       <c r="G32">
         <v>2.62</v>
@@ -3899,28 +3899,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M32">
-        <v>0.2073366</v>
+        <v>0.21424782</v>
       </c>
       <c r="N32">
-        <v>3.581847073469388</v>
+        <v>3.574935853469388</v>
       </c>
       <c r="O32">
-        <v>0.895461768367347</v>
+        <v>0.893733963367347</v>
       </c>
       <c r="P32">
-        <v>2.686385305102041</v>
+        <v>2.681201890102041</v>
       </c>
       <c r="Q32">
-        <v>3.856385305102041</v>
+        <v>3.851201890102041</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1176100141225065</v>
+        <v>0.1184538450757674</v>
       </c>
       <c r="T32">
-        <v>0.9884918740434327</v>
+        <v>1.000107524737245</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>18.27551755681046</v>
+        <v>17.68598473239722</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09342790310227952</v>
+        <v>0.09321129631880451</v>
       </c>
       <c r="C33">
-        <v>9.868864239724527</v>
+        <v>9.743976194693403</v>
       </c>
       <c r="D33">
-        <v>11.50826423972453</v>
+        <v>11.5207761946934</v>
       </c>
       <c r="E33">
-        <v>-7.5406</v>
+        <v>-7.403200000000001</v>
       </c>
       <c r="F33">
-        <v>4.2594</v>
+        <v>4.3968</v>
       </c>
       <c r="G33">
         <v>2.62</v>
@@ -3981,28 +3981,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M33">
-        <v>0.21424782</v>
+        <v>0.22115904</v>
       </c>
       <c r="N33">
-        <v>3.574935853469388</v>
+        <v>3.568024633469388</v>
       </c>
       <c r="O33">
-        <v>0.893733963367347</v>
+        <v>0.8920061583673471</v>
       </c>
       <c r="P33">
-        <v>2.681201890102041</v>
+        <v>2.676018475102041</v>
       </c>
       <c r="Q33">
-        <v>3.851201890102041</v>
+        <v>3.846018475102041</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1184538450757674</v>
+        <v>0.1193224945864772</v>
       </c>
       <c r="T33">
-        <v>1.000107524737245</v>
+        <v>1.01206481221617</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>17.68598473239722</v>
+        <v>17.13329770950981</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09321129631880451</v>
+        <v>0.09299468953532949</v>
       </c>
       <c r="C34">
-        <v>9.743976194693403</v>
+        <v>9.619115385638361</v>
       </c>
       <c r="D34">
-        <v>11.5207761946934</v>
+        <v>11.53331538563836</v>
       </c>
       <c r="E34">
-        <v>-7.403200000000001</v>
+        <v>-7.2658</v>
       </c>
       <c r="F34">
-        <v>4.3968</v>
+        <v>4.5342</v>
       </c>
       <c r="G34">
         <v>2.62</v>
@@ -4063,28 +4063,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M34">
-        <v>0.22115904</v>
+        <v>0.22807026</v>
       </c>
       <c r="N34">
-        <v>3.568024633469388</v>
+        <v>3.561113413469388</v>
       </c>
       <c r="O34">
-        <v>0.8920061583673471</v>
+        <v>0.8902783533673471</v>
       </c>
       <c r="P34">
-        <v>2.676018475102041</v>
+        <v>2.670835060102041</v>
       </c>
       <c r="Q34">
-        <v>3.846018475102041</v>
+        <v>3.840835060102041</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1193224945864772</v>
+        <v>0.1202170739333276</v>
       </c>
       <c r="T34">
-        <v>1.01206481221617</v>
+        <v>1.024379033649689</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>17.13329770950981</v>
+        <v>16.61410686982769</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09299468953532949</v>
+        <v>0.09277808275185449</v>
       </c>
       <c r="C35">
-        <v>9.619115385638361</v>
+        <v>9.494281901587055</v>
       </c>
       <c r="D35">
-        <v>11.53331538563836</v>
+        <v>11.54588190158706</v>
       </c>
       <c r="E35">
-        <v>-7.2658</v>
+        <v>-7.1284</v>
       </c>
       <c r="F35">
-        <v>4.5342</v>
+        <v>4.671600000000001</v>
       </c>
       <c r="G35">
         <v>2.62</v>
@@ -4145,28 +4145,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M35">
-        <v>0.22807026</v>
+        <v>0.23498148</v>
       </c>
       <c r="N35">
-        <v>3.561113413469388</v>
+        <v>3.554202193469388</v>
       </c>
       <c r="O35">
-        <v>0.8902783533673471</v>
+        <v>0.888550548367347</v>
       </c>
       <c r="P35">
-        <v>2.670835060102041</v>
+        <v>2.665651645102041</v>
       </c>
       <c r="Q35">
-        <v>3.840835060102041</v>
+        <v>3.835651645102041</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1202170739333276</v>
+        <v>0.1211387617452341</v>
       </c>
       <c r="T35">
-        <v>1.024379033649689</v>
+        <v>1.037066413308466</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>16.61410686982769</v>
+        <v>16.12545666777394</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09277808275185449</v>
+        <v>0.09256147596837948</v>
       </c>
       <c r="C36">
-        <v>9.494281901587055</v>
+        <v>9.369475831955572</v>
       </c>
       <c r="D36">
-        <v>11.54588190158706</v>
+        <v>11.55847583195557</v>
       </c>
       <c r="E36">
-        <v>-7.1284</v>
+        <v>-6.991000000000001</v>
       </c>
       <c r="F36">
-        <v>4.671600000000001</v>
+        <v>4.809</v>
       </c>
       <c r="G36">
         <v>2.62</v>
@@ -4227,28 +4227,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M36">
-        <v>0.23498148</v>
+        <v>0.2418927</v>
       </c>
       <c r="N36">
-        <v>3.554202193469388</v>
+        <v>3.547290973469388</v>
       </c>
       <c r="O36">
-        <v>0.888550548367347</v>
+        <v>0.886822743367347</v>
       </c>
       <c r="P36">
-        <v>2.665651645102041</v>
+        <v>2.660468230102041</v>
       </c>
       <c r="Q36">
-        <v>3.835651645102041</v>
+        <v>3.830468230102041</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1211387617452341</v>
+        <v>0.1220888091821223</v>
       </c>
       <c r="T36">
-        <v>1.037066413308466</v>
+        <v>1.050144173879822</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>16.12545666777394</v>
+        <v>15.66472933440897</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09256147596837948</v>
+        <v>0.09234486918490445</v>
       </c>
       <c r="C37">
-        <v>9.369475831955572</v>
+        <v>9.244697266550556</v>
       </c>
       <c r="D37">
-        <v>11.55847583195557</v>
+        <v>11.57109726655056</v>
       </c>
       <c r="E37">
-        <v>-6.991000000000001</v>
+        <v>-6.8536</v>
       </c>
       <c r="F37">
-        <v>4.809</v>
+        <v>4.946400000000001</v>
       </c>
       <c r="G37">
         <v>2.62</v>
@@ -4309,28 +4309,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M37">
-        <v>0.2418927</v>
+        <v>0.24880392</v>
       </c>
       <c r="N37">
-        <v>3.547290973469388</v>
+        <v>3.540379753469388</v>
       </c>
       <c r="O37">
-        <v>0.886822743367347</v>
+        <v>0.8850949383673471</v>
       </c>
       <c r="P37">
-        <v>2.660468230102041</v>
+        <v>2.655284815102041</v>
       </c>
       <c r="Q37">
-        <v>3.830468230102041</v>
+        <v>3.825284815102041</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1220888091821223</v>
+        <v>0.1230685456014132</v>
       </c>
       <c r="T37">
-        <v>1.050144173879822</v>
+        <v>1.063630614469032</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>15.66472933440897</v>
+        <v>15.22959796400872</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09234486918490446</v>
+        <v>0.09212826240142946</v>
       </c>
       <c r="C38">
-        <v>9.244697266550556</v>
+        <v>9.119946295571335</v>
       </c>
       <c r="D38">
-        <v>11.57109726655056</v>
+        <v>11.58374629557134</v>
       </c>
       <c r="E38">
-        <v>-6.853600000000001</v>
+        <v>-6.716200000000001</v>
       </c>
       <c r="F38">
-        <v>4.9464</v>
+        <v>5.0838</v>
       </c>
       <c r="G38">
         <v>2.62</v>
@@ -4391,28 +4391,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M38">
-        <v>0.24880392</v>
+        <v>0.25571514</v>
       </c>
       <c r="N38">
-        <v>3.540379753469388</v>
+        <v>3.533468533469388</v>
       </c>
       <c r="O38">
-        <v>0.8850949383673471</v>
+        <v>0.8833671333673471</v>
       </c>
       <c r="P38">
-        <v>2.655284815102041</v>
+        <v>2.650101400102041</v>
       </c>
       <c r="Q38">
-        <v>3.825284815102041</v>
+        <v>3.820101400102041</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1230685456014132</v>
+        <v>0.1240793847641737</v>
       </c>
       <c r="T38">
-        <v>1.063630614469032</v>
+        <v>1.077545196029328</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>15.22959796400872</v>
+        <v>14.8179872082247</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09212826240142946</v>
+        <v>0.09191165561795443</v>
       </c>
       <c r="C39">
-        <v>9.119946295571335</v>
+        <v>8.995223009612097</v>
       </c>
       <c r="D39">
-        <v>11.58374629557134</v>
+        <v>11.5964230096121</v>
       </c>
       <c r="E39">
-        <v>-6.716200000000001</v>
+        <v>-6.5788</v>
       </c>
       <c r="F39">
-        <v>5.0838</v>
+        <v>5.221200000000001</v>
       </c>
       <c r="G39">
         <v>2.62</v>
@@ -4473,28 +4473,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M39">
-        <v>0.25571514</v>
+        <v>0.26262636</v>
       </c>
       <c r="N39">
-        <v>3.533468533469388</v>
+        <v>3.526557313469388</v>
       </c>
       <c r="O39">
-        <v>0.8833671333673471</v>
+        <v>0.881639328367347</v>
       </c>
       <c r="P39">
-        <v>2.650101400102041</v>
+        <v>2.644917985102041</v>
       </c>
       <c r="Q39">
-        <v>3.820101400102041</v>
+        <v>3.814917985102041</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1240793847641737</v>
+        <v>0.125122831641862</v>
       </c>
       <c r="T39">
-        <v>1.077545196029328</v>
+        <v>1.091908635059311</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>14.8179872082247</v>
+        <v>14.42804017642931</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09191165561795443</v>
+        <v>0.09169504883447942</v>
       </c>
       <c r="C40">
-        <v>8.995223009612097</v>
+        <v>8.870527499664007</v>
       </c>
       <c r="D40">
-        <v>11.5964230096121</v>
+        <v>11.60912749966401</v>
       </c>
       <c r="E40">
-        <v>-6.5788</v>
+        <v>-6.441400000000001</v>
       </c>
       <c r="F40">
-        <v>5.221200000000001</v>
+        <v>5.3586</v>
       </c>
       <c r="G40">
         <v>2.62</v>
@@ -4555,28 +4555,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M40">
-        <v>0.26262636</v>
+        <v>0.26953758</v>
       </c>
       <c r="N40">
-        <v>3.526557313469388</v>
+        <v>3.519646093469388</v>
       </c>
       <c r="O40">
-        <v>0.881639328367347</v>
+        <v>0.879911523367347</v>
       </c>
       <c r="P40">
-        <v>2.644917985102041</v>
+        <v>2.639734570102041</v>
       </c>
       <c r="Q40">
-        <v>3.814917985102041</v>
+        <v>3.809734570102041</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.125122831641862</v>
+        <v>0.1262004898925892</v>
       </c>
       <c r="T40">
-        <v>1.091908635059311</v>
+        <v>1.106743006516506</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>14.42804017642931</v>
+        <v>14.05809042831574</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09169504883447942</v>
+        <v>0.09147844205100439</v>
       </c>
       <c r="C41">
-        <v>8.870527499664007</v>
+        <v>8.745859857117425</v>
       </c>
       <c r="D41">
-        <v>11.60912749966401</v>
+        <v>11.62185985711743</v>
       </c>
       <c r="E41">
-        <v>-6.441400000000001</v>
+        <v>-6.304</v>
       </c>
       <c r="F41">
-        <v>5.3586</v>
+        <v>5.496</v>
       </c>
       <c r="G41">
         <v>2.62</v>
@@ -4637,28 +4637,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M41">
-        <v>0.26953758</v>
+        <v>0.2764488</v>
       </c>
       <c r="N41">
-        <v>3.519646093469388</v>
+        <v>3.512734873469388</v>
       </c>
       <c r="O41">
-        <v>0.879911523367347</v>
+        <v>0.8781837183673471</v>
       </c>
       <c r="P41">
-        <v>2.639734570102041</v>
+        <v>2.634551155102042</v>
       </c>
       <c r="Q41">
-        <v>3.809734570102041</v>
+        <v>3.804551155102041</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1262004898925892</v>
+        <v>0.1273140700850073</v>
       </c>
       <c r="T41">
-        <v>1.106743006516506</v>
+        <v>1.122071857022275</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>14.05809042831574</v>
+        <v>13.70663816760785</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09147844205100439</v>
+        <v>0.0912618352675294</v>
       </c>
       <c r="C42">
-        <v>8.745859857117425</v>
+        <v>8.621220173764083</v>
       </c>
       <c r="D42">
-        <v>11.62185985711743</v>
+        <v>11.63462017376408</v>
       </c>
       <c r="E42">
-        <v>-6.304</v>
+        <v>-6.1666</v>
       </c>
       <c r="F42">
-        <v>5.496</v>
+        <v>5.633400000000001</v>
       </c>
       <c r="G42">
         <v>2.62</v>
@@ -4719,28 +4719,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M42">
-        <v>0.2764488</v>
+        <v>0.28336002</v>
       </c>
       <c r="N42">
-        <v>3.512734873469388</v>
+        <v>3.505823653469388</v>
       </c>
       <c r="O42">
-        <v>0.8781837183673471</v>
+        <v>0.8764559133673471</v>
       </c>
       <c r="P42">
-        <v>2.634551155102042</v>
+        <v>2.629367740102041</v>
       </c>
       <c r="Q42">
-        <v>3.804551155102041</v>
+        <v>3.799367740102041</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1273140700850073</v>
+        <v>0.1284653987585244</v>
       </c>
       <c r="T42">
-        <v>1.122071857022275</v>
+        <v>1.137920329579087</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>13.70663816760785</v>
+        <v>13.37232991961741</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0912618352675294</v>
+        <v>0.09104522848405439</v>
       </c>
       <c r="C43">
-        <v>8.621220173764083</v>
+        <v>8.496608541799283</v>
       </c>
       <c r="D43">
-        <v>11.63462017376408</v>
+        <v>11.64740854179928</v>
       </c>
       <c r="E43">
-        <v>-6.1666</v>
+        <v>-6.0292</v>
       </c>
       <c r="F43">
-        <v>5.633400000000001</v>
+        <v>5.7708</v>
       </c>
       <c r="G43">
         <v>2.62</v>
@@ -4801,28 +4801,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M43">
-        <v>0.28336002</v>
+        <v>0.29027124</v>
       </c>
       <c r="N43">
-        <v>3.505823653469388</v>
+        <v>3.498912433469388</v>
       </c>
       <c r="O43">
-        <v>0.8764559133673471</v>
+        <v>0.874728108367347</v>
       </c>
       <c r="P43">
-        <v>2.629367740102041</v>
+        <v>2.624184325102041</v>
       </c>
       <c r="Q43">
-        <v>3.799367740102041</v>
+        <v>3.794184325102041</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1284653987585244</v>
+        <v>0.1296564284207834</v>
       </c>
       <c r="T43">
-        <v>1.137920329579087</v>
+        <v>1.154315301189582</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>13.37232991961741</v>
+        <v>13.05394111200747</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0910452284840544</v>
+        <v>0.09131237170057938</v>
       </c>
       <c r="C44">
-        <v>8.496608541799281</v>
+        <v>8.343440564452628</v>
       </c>
       <c r="D44">
-        <v>11.64740854179928</v>
+        <v>11.63164056445263</v>
       </c>
       <c r="E44">
-        <v>-6.029200000000001</v>
+        <v>-5.891800000000001</v>
       </c>
       <c r="F44">
-        <v>5.770799999999999</v>
+        <v>5.9082</v>
       </c>
       <c r="G44">
         <v>2.62</v>
@@ -4883,45 +4883,45 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M44">
-        <v>0.29027124</v>
+        <v>0.30604476</v>
       </c>
       <c r="N44">
-        <v>3.498912433469388</v>
+        <v>3.483138913469388</v>
       </c>
       <c r="O44">
-        <v>0.874728108367347</v>
+        <v>0.8707847283673471</v>
       </c>
       <c r="P44">
-        <v>2.624184325102041</v>
+        <v>2.612354185102041</v>
       </c>
       <c r="Q44">
-        <v>3.794184325102041</v>
+        <v>3.782354185102041</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1296564284207834</v>
+        <v>0.1308892485975077</v>
       </c>
       <c r="T44">
-        <v>1.154315301189582</v>
+        <v>1.171285534961849</v>
       </c>
       <c r="U44">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y44">
-        <v>13.05394111200747</v>
+        <v>12.38114213577579</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09131237170057938</v>
+        <v>0.09110701491710438</v>
       </c>
       <c r="C45">
-        <v>8.343440564452628</v>
+        <v>8.218157833344637</v>
       </c>
       <c r="D45">
-        <v>11.63164056445263</v>
+        <v>11.64375783334464</v>
       </c>
       <c r="E45">
-        <v>-5.891800000000001</v>
+        <v>-5.7544</v>
       </c>
       <c r="F45">
-        <v>5.9082</v>
+        <v>6.0456</v>
       </c>
       <c r="G45">
         <v>2.62</v>
@@ -4965,28 +4965,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M45">
-        <v>0.30604476</v>
+        <v>0.31316208</v>
       </c>
       <c r="N45">
-        <v>3.483138913469388</v>
+        <v>3.476021593469388</v>
       </c>
       <c r="O45">
-        <v>0.8707847283673471</v>
+        <v>0.869005398367347</v>
       </c>
       <c r="P45">
-        <v>2.612354185102041</v>
+        <v>2.607016195102041</v>
       </c>
       <c r="Q45">
-        <v>3.782354185102041</v>
+        <v>3.777016195102041</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1308892485975077</v>
+        <v>0.1321660980662578</v>
       </c>
       <c r="T45">
-        <v>1.171285534961849</v>
+        <v>1.188861848511696</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>12.38114213577579</v>
+        <v>12.09975254178088</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09110701491710438</v>
+        <v>0.09090165813362935</v>
       </c>
       <c r="C46">
-        <v>8.218157833344637</v>
+        <v>8.092900374909487</v>
       </c>
       <c r="D46">
-        <v>11.64375783334464</v>
+        <v>11.65590037490949</v>
       </c>
       <c r="E46">
-        <v>-5.7544</v>
+        <v>-5.617000000000001</v>
       </c>
       <c r="F46">
-        <v>6.0456</v>
+        <v>6.183</v>
       </c>
       <c r="G46">
         <v>2.62</v>
@@ -5047,28 +5047,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M46">
-        <v>0.31316208</v>
+        <v>0.3202794</v>
       </c>
       <c r="N46">
-        <v>3.476021593469388</v>
+        <v>3.468904273469388</v>
       </c>
       <c r="O46">
-        <v>0.869005398367347</v>
+        <v>0.8672260683673471</v>
       </c>
       <c r="P46">
-        <v>2.607016195102041</v>
+        <v>2.601678205102041</v>
       </c>
       <c r="Q46">
-        <v>3.777016195102041</v>
+        <v>3.771678205102041</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1321660980662578</v>
+        <v>0.1334893784247806</v>
       </c>
       <c r="T46">
-        <v>1.188861848511696</v>
+        <v>1.207077300736084</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>12.09975254178088</v>
+        <v>11.83086915196353</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09090165813362935</v>
+        <v>0.09069630135015436</v>
       </c>
       <c r="C47">
-        <v>8.092900374909487</v>
+        <v>7.96766826829555</v>
       </c>
       <c r="D47">
-        <v>11.65590037490949</v>
+        <v>11.66806826829555</v>
       </c>
       <c r="E47">
-        <v>-5.617000000000001</v>
+        <v>-5.4796</v>
       </c>
       <c r="F47">
-        <v>6.183</v>
+        <v>6.3204</v>
       </c>
       <c r="G47">
         <v>2.62</v>
@@ -5129,28 +5129,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M47">
-        <v>0.3202794</v>
+        <v>0.32739672</v>
       </c>
       <c r="N47">
-        <v>3.468904273469388</v>
+        <v>3.461786953469388</v>
       </c>
       <c r="O47">
-        <v>0.8672260683673471</v>
+        <v>0.8654467383673471</v>
       </c>
       <c r="P47">
-        <v>2.601678205102041</v>
+        <v>2.596340215102041</v>
       </c>
       <c r="Q47">
-        <v>3.771678205102041</v>
+        <v>3.766340215102041</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1334893784247806</v>
+        <v>0.1348616691669525</v>
       </c>
       <c r="T47">
-        <v>1.207077300736084</v>
+        <v>1.225967399339152</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.83086915196353</v>
+        <v>11.57367634431215</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09069630135015436</v>
+        <v>0.09049094456667933</v>
       </c>
       <c r="C48">
-        <v>7.96766826829555</v>
+        <v>7.842461592982046</v>
       </c>
       <c r="D48">
-        <v>11.66806826829555</v>
+        <v>11.68026159298205</v>
       </c>
       <c r="E48">
-        <v>-5.4796</v>
+        <v>-5.3422</v>
       </c>
       <c r="F48">
-        <v>6.3204</v>
+        <v>6.457800000000001</v>
       </c>
       <c r="G48">
         <v>2.62</v>
@@ -5211,28 +5211,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M48">
-        <v>0.32739672</v>
+        <v>0.33451404</v>
       </c>
       <c r="N48">
-        <v>3.461786953469388</v>
+        <v>3.454669633469388</v>
       </c>
       <c r="O48">
-        <v>0.8654467383673471</v>
+        <v>0.863667408367347</v>
       </c>
       <c r="P48">
-        <v>2.596340215102041</v>
+        <v>2.591002225102041</v>
       </c>
       <c r="Q48">
-        <v>3.766340215102041</v>
+        <v>3.761002225102041</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1348616691669525</v>
+        <v>0.1362857444654327</v>
       </c>
       <c r="T48">
-        <v>1.225967399339152</v>
+        <v>1.245570331851771</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.57367634431215</v>
+        <v>11.32742791145444</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09049094456667933</v>
+        <v>0.09028558778320431</v>
       </c>
       <c r="C49">
-        <v>7.842461592982046</v>
+        <v>7.717280428780772</v>
       </c>
       <c r="D49">
-        <v>11.68026159298205</v>
+        <v>11.69248042878077</v>
       </c>
       <c r="E49">
-        <v>-5.3422</v>
+        <v>-5.2048</v>
       </c>
       <c r="F49">
-        <v>6.457800000000001</v>
+        <v>6.595200000000001</v>
       </c>
       <c r="G49">
         <v>2.62</v>
@@ -5293,28 +5293,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M49">
-        <v>0.33451404</v>
+        <v>0.3416313600000001</v>
       </c>
       <c r="N49">
-        <v>3.454669633469388</v>
+        <v>3.447552313469388</v>
       </c>
       <c r="O49">
-        <v>0.863667408367347</v>
+        <v>0.861888078367347</v>
       </c>
       <c r="P49">
-        <v>2.591002225102041</v>
+        <v>2.585664235102041</v>
       </c>
       <c r="Q49">
-        <v>3.761002225102041</v>
+        <v>3.755664235102041</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1362857444654327</v>
+        <v>0.1377645918907775</v>
       </c>
       <c r="T49">
-        <v>1.245570331851771</v>
+        <v>1.265927223307182</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>11.32742791145444</v>
+        <v>11.09143982996581</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09028558778320431</v>
+        <v>0.09008023099972931</v>
       </c>
       <c r="C50">
-        <v>7.717280428780773</v>
+        <v>7.592124855837843</v>
       </c>
       <c r="D50">
-        <v>11.69248042878077</v>
+        <v>11.70472485583784</v>
       </c>
       <c r="E50">
-        <v>-5.204800000000001</v>
+        <v>-5.067400000000001</v>
       </c>
       <c r="F50">
-        <v>6.5952</v>
+        <v>6.7326</v>
       </c>
       <c r="G50">
         <v>2.62</v>
@@ -5375,28 +5375,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M50">
-        <v>0.34163136</v>
+        <v>0.34874868</v>
       </c>
       <c r="N50">
-        <v>3.447552313469388</v>
+        <v>3.440434993469388</v>
       </c>
       <c r="O50">
-        <v>0.861888078367347</v>
+        <v>0.8601087483673471</v>
       </c>
       <c r="P50">
-        <v>2.585664235102041</v>
+        <v>2.580326245102041</v>
       </c>
       <c r="Q50">
-        <v>3.755664235102041</v>
+        <v>3.750326245102041</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1377645918907775</v>
+        <v>0.1393014333328026</v>
       </c>
       <c r="T50">
-        <v>1.265927223307182</v>
+        <v>1.287082424231433</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>11.09143982996581</v>
+        <v>10.86508391506855</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09008023099972931</v>
+        <v>0.08987487421625429</v>
       </c>
       <c r="C51">
-        <v>7.592124855837843</v>
+        <v>7.466994954635436</v>
       </c>
       <c r="D51">
-        <v>11.70472485583784</v>
+        <v>11.71699495463544</v>
       </c>
       <c r="E51">
-        <v>-5.067400000000001</v>
+        <v>-4.930000000000001</v>
       </c>
       <c r="F51">
-        <v>6.7326</v>
+        <v>6.87</v>
       </c>
       <c r="G51">
         <v>2.62</v>
@@ -5457,28 +5457,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M51">
-        <v>0.34874868</v>
+        <v>0.355866</v>
       </c>
       <c r="N51">
-        <v>3.440434993469388</v>
+        <v>3.433317673469388</v>
       </c>
       <c r="O51">
-        <v>0.8601087483673471</v>
+        <v>0.8583294183673471</v>
       </c>
       <c r="P51">
-        <v>2.580326245102041</v>
+        <v>2.574988255102041</v>
       </c>
       <c r="Q51">
-        <v>3.750326245102041</v>
+        <v>3.744988255102041</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1393014333328026</v>
+        <v>0.1408997484325086</v>
       </c>
       <c r="T51">
-        <v>1.287082424231433</v>
+        <v>1.309083833192654</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.86508391506855</v>
+        <v>10.64778223676718</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08987487421625429</v>
+        <v>0.08966951743277927</v>
       </c>
       <c r="C52">
-        <v>7.466994954635436</v>
+        <v>7.341890805993572</v>
       </c>
       <c r="D52">
-        <v>11.71699495463544</v>
+        <v>11.72929080599357</v>
       </c>
       <c r="E52">
-        <v>-4.930000000000001</v>
+        <v>-4.7926</v>
       </c>
       <c r="F52">
-        <v>6.87</v>
+        <v>7.007400000000001</v>
       </c>
       <c r="G52">
         <v>2.62</v>
@@ -5539,28 +5539,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M52">
-        <v>0.355866</v>
+        <v>0.36298332</v>
       </c>
       <c r="N52">
-        <v>3.433317673469388</v>
+        <v>3.426200353469388</v>
       </c>
       <c r="O52">
-        <v>0.8583294183673471</v>
+        <v>0.856550088367347</v>
       </c>
       <c r="P52">
-        <v>2.574988255102041</v>
+        <v>2.569650265102041</v>
       </c>
       <c r="Q52">
-        <v>3.744988255102041</v>
+        <v>3.739650265102041</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1408997484325086</v>
+        <v>0.142563300883223</v>
       </c>
       <c r="T52">
-        <v>1.309083833192654</v>
+        <v>1.33198325884617</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.64778223676718</v>
+        <v>10.439002192909</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08966951743277927</v>
+        <v>0.08946416064930426</v>
       </c>
       <c r="C53">
-        <v>7.341890805993572</v>
+        <v>7.216812491071874</v>
       </c>
       <c r="D53">
-        <v>11.72929080599357</v>
+        <v>11.74161249107187</v>
       </c>
       <c r="E53">
-        <v>-4.7926</v>
+        <v>-4.655200000000001</v>
       </c>
       <c r="F53">
-        <v>7.007400000000001</v>
+        <v>7.1448</v>
       </c>
       <c r="G53">
         <v>2.62</v>
@@ -5621,28 +5621,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M53">
-        <v>0.36298332</v>
+        <v>0.37010064</v>
       </c>
       <c r="N53">
-        <v>3.426200353469388</v>
+        <v>3.419083033469388</v>
       </c>
       <c r="O53">
-        <v>0.856550088367347</v>
+        <v>0.8547707583673471</v>
       </c>
       <c r="P53">
-        <v>2.569650265102041</v>
+        <v>2.564312275102041</v>
       </c>
       <c r="Q53">
-        <v>3.739650265102041</v>
+        <v>3.734312275102041</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.142563300883223</v>
+        <v>0.1442961680193839</v>
       </c>
       <c r="T53">
-        <v>1.33198325884617</v>
+        <v>1.355836827235249</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.439002192909</v>
+        <v>10.23825215073767</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08946416064930426</v>
+        <v>0.08925880386582925</v>
       </c>
       <c r="C54">
-        <v>7.216812491071874</v>
+        <v>7.091760091371355</v>
       </c>
       <c r="D54">
-        <v>11.74161249107187</v>
+        <v>11.75396009137135</v>
       </c>
       <c r="E54">
-        <v>-4.655200000000001</v>
+        <v>-4.5178</v>
       </c>
       <c r="F54">
-        <v>7.1448</v>
+        <v>7.2822</v>
       </c>
       <c r="G54">
         <v>2.62</v>
@@ -5703,28 +5703,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M54">
-        <v>0.37010064</v>
+        <v>0.37721796</v>
       </c>
       <c r="N54">
-        <v>3.419083033469388</v>
+        <v>3.411965713469388</v>
       </c>
       <c r="O54">
-        <v>0.8547707583673471</v>
+        <v>0.8529914283673471</v>
       </c>
       <c r="P54">
-        <v>2.564312275102041</v>
+        <v>2.558974285102041</v>
       </c>
       <c r="Q54">
-        <v>3.734312275102041</v>
+        <v>3.728974285102041</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1442961680193839</v>
+        <v>0.1461027741826154</v>
       </c>
       <c r="T54">
-        <v>1.355836827235249</v>
+        <v>1.380705441087693</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>10.23825215073767</v>
+        <v>10.04507758185583</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08925880386582925</v>
+        <v>0.08905344708235423</v>
       </c>
       <c r="C55">
-        <v>7.091760091371355</v>
+        <v>6.966733688736221</v>
       </c>
       <c r="D55">
-        <v>11.75396009137135</v>
+        <v>11.76633368873622</v>
       </c>
       <c r="E55">
-        <v>-4.5178</v>
+        <v>-4.3804</v>
       </c>
       <c r="F55">
-        <v>7.2822</v>
+        <v>7.419600000000001</v>
       </c>
       <c r="G55">
         <v>2.62</v>
@@ -5785,28 +5785,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M55">
-        <v>0.37721796</v>
+        <v>0.3843352800000001</v>
       </c>
       <c r="N55">
-        <v>3.411965713469388</v>
+        <v>3.404848393469388</v>
       </c>
       <c r="O55">
-        <v>0.8529914283673471</v>
+        <v>0.851212098367347</v>
       </c>
       <c r="P55">
-        <v>2.558974285102041</v>
+        <v>2.553636295102041</v>
       </c>
       <c r="Q55">
-        <v>3.728974285102041</v>
+        <v>3.723636295102041</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1461027741826154</v>
+        <v>0.1479879284399005</v>
       </c>
       <c r="T55">
-        <v>1.380705441087693</v>
+        <v>1.406655299020678</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.04507758185583</v>
+        <v>9.859057626636273</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08905344708235423</v>
+        <v>0.08954934029887922</v>
       </c>
       <c r="C56">
-        <v>6.966733688736221</v>
+        <v>6.799498456112241</v>
       </c>
       <c r="D56">
-        <v>11.76633368873622</v>
+        <v>11.73649845611224</v>
       </c>
       <c r="E56">
-        <v>-4.3804</v>
+        <v>-4.243</v>
       </c>
       <c r="F56">
-        <v>7.419600000000001</v>
+        <v>7.557</v>
       </c>
       <c r="G56">
         <v>2.62</v>
@@ -5867,45 +5867,45 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M56">
-        <v>0.3843352800000001</v>
+        <v>0.4042995</v>
       </c>
       <c r="N56">
-        <v>3.404848393469388</v>
+        <v>3.384884173469388</v>
       </c>
       <c r="O56">
-        <v>0.851212098367347</v>
+        <v>0.846221043367347</v>
       </c>
       <c r="P56">
-        <v>2.553636295102041</v>
+        <v>2.538663130102041</v>
       </c>
       <c r="Q56">
-        <v>3.723636295102041</v>
+        <v>3.708663130102041</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1479879284399005</v>
+        <v>0.1499568673308427</v>
       </c>
       <c r="T56">
-        <v>1.406655299020678</v>
+        <v>1.433758483972907</v>
       </c>
       <c r="U56">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>9.859057626636273</v>
+        <v>9.372219538904668</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08954934029887922</v>
+        <v>0.08935673351540421</v>
       </c>
       <c r="C57">
-        <v>6.799498456112241</v>
+        <v>6.673668583805477</v>
       </c>
       <c r="D57">
-        <v>11.73649845611224</v>
+        <v>11.74806858380548</v>
       </c>
       <c r="E57">
-        <v>-4.243</v>
+        <v>-4.1056</v>
       </c>
       <c r="F57">
-        <v>7.557</v>
+        <v>7.694400000000001</v>
       </c>
       <c r="G57">
         <v>2.62</v>
@@ -5949,28 +5949,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M57">
-        <v>0.4042995</v>
+        <v>0.4116504</v>
       </c>
       <c r="N57">
-        <v>3.384884173469388</v>
+        <v>3.377533273469388</v>
       </c>
       <c r="O57">
-        <v>0.846221043367347</v>
+        <v>0.844383318367347</v>
       </c>
       <c r="P57">
-        <v>2.538663130102041</v>
+        <v>2.533149955102041</v>
       </c>
       <c r="Q57">
-        <v>3.708663130102041</v>
+        <v>3.703149955102041</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1499568673308427</v>
+        <v>0.1520153034441005</v>
       </c>
       <c r="T57">
-        <v>1.433758483972907</v>
+        <v>1.46209363187751</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>9.372219538904668</v>
+        <v>9.204858475709942</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08935673351540421</v>
+        <v>0.08916412673192922</v>
       </c>
       <c r="C58">
-        <v>6.673668583805477</v>
+        <v>6.547861546240405</v>
       </c>
       <c r="D58">
-        <v>11.74806858380548</v>
+        <v>11.75966154624041</v>
       </c>
       <c r="E58">
-        <v>-4.1056</v>
+        <v>-3.9682</v>
       </c>
       <c r="F58">
-        <v>7.694400000000001</v>
+        <v>7.831800000000001</v>
       </c>
       <c r="G58">
         <v>2.62</v>
@@ -6031,28 +6031,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M58">
-        <v>0.4116504</v>
+        <v>0.4190013000000001</v>
       </c>
       <c r="N58">
-        <v>3.377533273469388</v>
+        <v>3.370182373469388</v>
       </c>
       <c r="O58">
-        <v>0.844383318367347</v>
+        <v>0.842545593367347</v>
       </c>
       <c r="P58">
-        <v>2.533149955102041</v>
+        <v>2.527636780102041</v>
       </c>
       <c r="Q58">
-        <v>3.703149955102041</v>
+        <v>3.697636780102041</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1520153034441005</v>
+        <v>0.1541694807719284</v>
       </c>
       <c r="T58">
-        <v>1.46209363187751</v>
+        <v>1.491746693638141</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>9.204858475709942</v>
+        <v>9.043369730522047</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08916412673192922</v>
+        <v>0.08897151994845419</v>
       </c>
       <c r="C59">
-        <v>6.547861546240405</v>
+        <v>6.422077411083578</v>
       </c>
       <c r="D59">
-        <v>11.75966154624041</v>
+        <v>11.77127741108358</v>
       </c>
       <c r="E59">
-        <v>-3.9682</v>
+        <v>-3.8308</v>
       </c>
       <c r="F59">
-        <v>7.831800000000001</v>
+        <v>7.969200000000001</v>
       </c>
       <c r="G59">
         <v>2.62</v>
@@ -6113,28 +6113,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M59">
-        <v>0.4190013000000001</v>
+        <v>0.4263522</v>
       </c>
       <c r="N59">
-        <v>3.370182373469388</v>
+        <v>3.362831473469388</v>
       </c>
       <c r="O59">
-        <v>0.842545593367347</v>
+        <v>0.840707868367347</v>
       </c>
       <c r="P59">
-        <v>2.527636780102041</v>
+        <v>2.522123605102041</v>
       </c>
       <c r="Q59">
-        <v>3.697636780102041</v>
+        <v>3.692123605102041</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1541694807719284</v>
+        <v>0.15642623797251</v>
       </c>
       <c r="T59">
-        <v>1.491746693638141</v>
+        <v>1.522811805958802</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>9.043369730522047</v>
+        <v>8.887449562754426</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0889715199484542</v>
+        <v>0.08877891316497918</v>
       </c>
       <c r="C60">
-        <v>6.422077411083575</v>
+        <v>6.296316246269171</v>
       </c>
       <c r="D60">
-        <v>11.77127741108358</v>
+        <v>11.78291624626917</v>
       </c>
       <c r="E60">
-        <v>-3.830800000000001</v>
+        <v>-3.6934</v>
       </c>
       <c r="F60">
-        <v>7.9692</v>
+        <v>8.1066</v>
       </c>
       <c r="G60">
         <v>2.62</v>
@@ -6195,28 +6195,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M60">
-        <v>0.4263522</v>
+        <v>0.4337031</v>
       </c>
       <c r="N60">
-        <v>3.362831473469388</v>
+        <v>3.355480573469388</v>
       </c>
       <c r="O60">
-        <v>0.840707868367347</v>
+        <v>0.8388701433673471</v>
       </c>
       <c r="P60">
-        <v>2.522123605102041</v>
+        <v>2.516610430102041</v>
       </c>
       <c r="Q60">
-        <v>3.692123605102041</v>
+        <v>3.686610430102041</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.15642623797251</v>
+        <v>0.1587930808901931</v>
       </c>
       <c r="T60">
-        <v>1.522811805958802</v>
+        <v>1.555392289612178</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.887449562754428</v>
+        <v>8.736814824402657</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08877891316497918</v>
+        <v>0.08858630638150418</v>
       </c>
       <c r="C61">
-        <v>6.296316246269171</v>
+        <v>6.170578120000314</v>
       </c>
       <c r="D61">
-        <v>11.78291624626917</v>
+        <v>11.79457812000032</v>
       </c>
       <c r="E61">
-        <v>-3.6934</v>
+        <v>-3.556000000000001</v>
       </c>
       <c r="F61">
-        <v>8.1066</v>
+        <v>8.244</v>
       </c>
       <c r="G61">
         <v>2.62</v>
@@ -6277,28 +6277,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M61">
-        <v>0.4337031</v>
+        <v>0.441054</v>
       </c>
       <c r="N61">
-        <v>3.355480573469388</v>
+        <v>3.348129673469388</v>
       </c>
       <c r="O61">
-        <v>0.8388701433673471</v>
+        <v>0.8370324183673471</v>
       </c>
       <c r="P61">
-        <v>2.516610430102041</v>
+        <v>2.511097255102041</v>
       </c>
       <c r="Q61">
-        <v>3.686610430102041</v>
+        <v>3.681097255102041</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1587930808901931</v>
+        <v>0.1612782659537604</v>
       </c>
       <c r="T61">
-        <v>1.555392289612178</v>
+        <v>1.589601797448223</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.736814824402657</v>
+        <v>8.591201243995947</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08858630638150418</v>
+        <v>0.08839369959802916</v>
       </c>
       <c r="C62">
-        <v>6.170578120000314</v>
+        <v>6.044863100750405</v>
       </c>
       <c r="D62">
-        <v>11.79457812000032</v>
+        <v>11.8062631007504</v>
       </c>
       <c r="E62">
-        <v>-3.556000000000001</v>
+        <v>-3.418600000000001</v>
       </c>
       <c r="F62">
-        <v>8.244</v>
+        <v>8.381399999999999</v>
       </c>
       <c r="G62">
         <v>2.62</v>
@@ -6359,28 +6359,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M62">
-        <v>0.441054</v>
+        <v>0.4484048999999999</v>
       </c>
       <c r="N62">
-        <v>3.348129673469388</v>
+        <v>3.340778773469388</v>
       </c>
       <c r="O62">
-        <v>0.8370324183673471</v>
+        <v>0.8351946933673471</v>
       </c>
       <c r="P62">
-        <v>2.511097255102041</v>
+        <v>2.505584080102041</v>
       </c>
       <c r="Q62">
-        <v>3.681097255102041</v>
+        <v>3.675584080102041</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1612782659537604</v>
+        <v>0.163890896405203</v>
       </c>
       <c r="T62">
-        <v>1.589601797448223</v>
+        <v>1.62556563901945</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.591201243995947</v>
+        <v>8.450361879340276</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08839369959802916</v>
+        <v>0.08820109281455414</v>
       </c>
       <c r="C63">
-        <v>6.044863100750405</v>
+        <v>5.919171257264464</v>
       </c>
       <c r="D63">
-        <v>11.8062631007504</v>
+        <v>11.81797125726447</v>
       </c>
       <c r="E63">
-        <v>-3.418600000000001</v>
+        <v>-3.2812</v>
       </c>
       <c r="F63">
-        <v>8.381399999999999</v>
+        <v>8.518800000000001</v>
       </c>
       <c r="G63">
         <v>2.62</v>
@@ -6441,28 +6441,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M63">
-        <v>0.4484048999999999</v>
+        <v>0.4557558</v>
       </c>
       <c r="N63">
-        <v>3.340778773469388</v>
+        <v>3.333427873469388</v>
       </c>
       <c r="O63">
-        <v>0.8351946933673471</v>
+        <v>0.8333569683673471</v>
       </c>
       <c r="P63">
-        <v>2.505584080102041</v>
+        <v>2.500070905102041</v>
       </c>
       <c r="Q63">
-        <v>3.675584080102041</v>
+        <v>3.670070905102041</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.163890896405203</v>
+        <v>0.1666410337225109</v>
       </c>
       <c r="T63">
-        <v>1.62556563901945</v>
+        <v>1.663422314357583</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.450361879340276</v>
+        <v>8.314065719996076</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08820109281455414</v>
+        <v>0.08800848603107914</v>
       </c>
       <c r="C64">
-        <v>5.919171257264464</v>
+        <v>5.793502658560479</v>
       </c>
       <c r="D64">
-        <v>11.81797125726447</v>
+        <v>11.82970265856048</v>
       </c>
       <c r="E64">
-        <v>-3.2812</v>
+        <v>-3.143800000000001</v>
       </c>
       <c r="F64">
-        <v>8.518800000000001</v>
+        <v>8.6562</v>
       </c>
       <c r="G64">
         <v>2.62</v>
@@ -6523,28 +6523,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M64">
-        <v>0.4557558</v>
+        <v>0.4631067</v>
       </c>
       <c r="N64">
-        <v>3.333427873469388</v>
+        <v>3.326076973469388</v>
       </c>
       <c r="O64">
-        <v>0.8333569683673471</v>
+        <v>0.8315192433673471</v>
       </c>
       <c r="P64">
-        <v>2.500070905102041</v>
+        <v>2.494557730102041</v>
       </c>
       <c r="Q64">
-        <v>3.670070905102041</v>
+        <v>3.664557730102041</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1666410337225109</v>
+        <v>0.1695398271110247</v>
       </c>
       <c r="T64">
-        <v>1.663422314357583</v>
+        <v>1.703325296470751</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.314065719996076</v>
+        <v>8.182096422853283</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08800848603107914</v>
+        <v>0.08781587924760413</v>
       </c>
       <c r="C65">
-        <v>5.793502658560479</v>
+        <v>5.667857373930753</v>
       </c>
       <c r="D65">
-        <v>11.82970265856048</v>
+        <v>11.84145737393075</v>
       </c>
       <c r="E65">
-        <v>-3.143800000000001</v>
+        <v>-3.006400000000001</v>
       </c>
       <c r="F65">
-        <v>8.6562</v>
+        <v>8.7936</v>
       </c>
       <c r="G65">
         <v>2.62</v>
@@ -6605,28 +6605,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M65">
-        <v>0.4631067</v>
+        <v>0.4704576</v>
       </c>
       <c r="N65">
-        <v>3.326076973469388</v>
+        <v>3.318726073469388</v>
       </c>
       <c r="O65">
-        <v>0.8315192433673471</v>
+        <v>0.829681518367347</v>
       </c>
       <c r="P65">
-        <v>2.494557730102041</v>
+        <v>2.489044555102041</v>
       </c>
       <c r="Q65">
-        <v>3.664557730102041</v>
+        <v>3.659044555102041</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1695398271110247</v>
+        <v>0.1725996645766781</v>
       </c>
       <c r="T65">
-        <v>1.703325296470751</v>
+        <v>1.745445110923539</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.182096422853283</v>
+        <v>8.0542511662462</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08781587924760413</v>
+        <v>0.08762327246412911</v>
       </c>
       <c r="C66">
-        <v>5.667857373930753</v>
+        <v>5.542235472943283</v>
       </c>
       <c r="D66">
-        <v>11.84145737393075</v>
+        <v>11.85323547294328</v>
       </c>
       <c r="E66">
-        <v>-3.006400000000001</v>
+        <v>-2.869</v>
       </c>
       <c r="F66">
-        <v>8.7936</v>
+        <v>8.931000000000001</v>
       </c>
       <c r="G66">
         <v>2.62</v>
@@ -6687,28 +6687,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M66">
-        <v>0.4704576</v>
+        <v>0.4778085</v>
       </c>
       <c r="N66">
-        <v>3.318726073469388</v>
+        <v>3.311375173469388</v>
       </c>
       <c r="O66">
-        <v>0.829681518367347</v>
+        <v>0.827843793367347</v>
       </c>
       <c r="P66">
-        <v>2.489044555102041</v>
+        <v>2.483531380102041</v>
       </c>
       <c r="Q66">
-        <v>3.659044555102041</v>
+        <v>3.653531380102041</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1725996645766781</v>
+        <v>0.1758343498975118</v>
       </c>
       <c r="T66">
-        <v>1.745445110923539</v>
+        <v>1.789971771916487</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.0542511662462</v>
+        <v>7.930339609842411</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08762327246412911</v>
+        <v>0.08743066568065409</v>
       </c>
       <c r="C67">
-        <v>5.542235472943283</v>
+        <v>5.416637025443116</v>
       </c>
       <c r="D67">
-        <v>11.85323547294328</v>
+        <v>11.86503702544312</v>
       </c>
       <c r="E67">
-        <v>-2.869</v>
+        <v>-2.7316</v>
       </c>
       <c r="F67">
-        <v>8.931000000000001</v>
+        <v>9.0684</v>
       </c>
       <c r="G67">
         <v>2.62</v>
@@ -6769,28 +6769,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M67">
-        <v>0.4778085</v>
+        <v>0.4851594</v>
       </c>
       <c r="N67">
-        <v>3.311375173469388</v>
+        <v>3.304024273469388</v>
       </c>
       <c r="O67">
-        <v>0.827843793367347</v>
+        <v>0.826006068367347</v>
       </c>
       <c r="P67">
-        <v>2.483531380102041</v>
+        <v>2.478018205102041</v>
       </c>
       <c r="Q67">
-        <v>3.653531380102041</v>
+        <v>3.648018205102041</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1758343498975118</v>
+        <v>0.1792593108254532</v>
       </c>
       <c r="T67">
-        <v>1.789971771916487</v>
+        <v>1.83711764826196</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.930339609842411</v>
+        <v>7.810182949087223</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08743066568065409</v>
+        <v>0.08723805889717909</v>
       </c>
       <c r="C68">
-        <v>5.416637025443116</v>
+        <v>5.291062101553742</v>
       </c>
       <c r="D68">
-        <v>11.86503702544312</v>
+        <v>11.87686210155374</v>
       </c>
       <c r="E68">
-        <v>-2.7316</v>
+        <v>-2.594200000000001</v>
       </c>
       <c r="F68">
-        <v>9.0684</v>
+        <v>9.2058</v>
       </c>
       <c r="G68">
         <v>2.62</v>
@@ -6851,28 +6851,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M68">
-        <v>0.4851594</v>
+        <v>0.4925103</v>
       </c>
       <c r="N68">
-        <v>3.304024273469388</v>
+        <v>3.296673373469388</v>
       </c>
       <c r="O68">
-        <v>0.826006068367347</v>
+        <v>0.824168343367347</v>
       </c>
       <c r="P68">
-        <v>2.478018205102041</v>
+        <v>2.472505030102041</v>
       </c>
       <c r="Q68">
-        <v>3.648018205102041</v>
+        <v>3.642505030102041</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1792593108254532</v>
+        <v>0.1828918451429669</v>
       </c>
       <c r="T68">
-        <v>1.83711764826196</v>
+        <v>1.887120850446554</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.810182949087223</v>
+        <v>7.693613054324728</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08723805889717909</v>
+        <v>0.08745345211370406</v>
       </c>
       <c r="C69">
-        <v>5.291062101553742</v>
+        <v>5.140439611911843</v>
       </c>
       <c r="D69">
-        <v>11.87686210155374</v>
+        <v>11.86363961191184</v>
       </c>
       <c r="E69">
-        <v>-2.594200000000001</v>
+        <v>-2.456799999999999</v>
       </c>
       <c r="F69">
-        <v>9.2058</v>
+        <v>9.343200000000001</v>
       </c>
       <c r="G69">
         <v>2.62</v>
@@ -6933,45 +6933,45 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M69">
-        <v>0.4925103</v>
+        <v>0.50733576</v>
       </c>
       <c r="N69">
-        <v>3.296673373469388</v>
+        <v>3.281847913469388</v>
       </c>
       <c r="O69">
-        <v>0.824168343367347</v>
+        <v>0.820461978367347</v>
       </c>
       <c r="P69">
-        <v>2.472505030102041</v>
+        <v>2.461385935102041</v>
       </c>
       <c r="Q69">
-        <v>3.642505030102041</v>
+        <v>3.631385935102041</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1828918451429669</v>
+        <v>0.1867514128553252</v>
       </c>
       <c r="T69">
-        <v>1.887120850446554</v>
+        <v>1.940249252767684</v>
       </c>
       <c r="U69">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y69">
-        <v>7.693613054324728</v>
+        <v>7.468788861777431</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08745345211370406</v>
+        <v>0.08726684533022905</v>
       </c>
       <c r="C70">
-        <v>5.140439611911843</v>
+        <v>5.014493263178112</v>
       </c>
       <c r="D70">
-        <v>11.86363961191184</v>
+        <v>11.87509326317811</v>
       </c>
       <c r="E70">
-        <v>-2.456799999999999</v>
+        <v>-2.3194</v>
       </c>
       <c r="F70">
-        <v>9.343200000000001</v>
+        <v>9.480600000000001</v>
       </c>
       <c r="G70">
         <v>2.62</v>
@@ -7015,28 +7015,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M70">
-        <v>0.50733576</v>
+        <v>0.5147965800000001</v>
       </c>
       <c r="N70">
-        <v>3.281847913469388</v>
+        <v>3.274387093469388</v>
       </c>
       <c r="O70">
-        <v>0.820461978367347</v>
+        <v>0.818596773367347</v>
       </c>
       <c r="P70">
-        <v>2.461385935102041</v>
+        <v>2.455790320102041</v>
       </c>
       <c r="Q70">
-        <v>3.631385935102041</v>
+        <v>3.625790320102041</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1867514128553252</v>
+        <v>0.1908599849362228</v>
       </c>
       <c r="T70">
-        <v>1.940249252767684</v>
+        <v>1.996805293948243</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.468788861777431</v>
+        <v>7.360545544940076</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08726684533022905</v>
+        <v>0.08708023854675404</v>
       </c>
       <c r="C71">
-        <v>5.014493263178112</v>
+        <v>4.888569051479317</v>
       </c>
       <c r="D71">
-        <v>11.87509326317811</v>
+        <v>11.88656905147932</v>
       </c>
       <c r="E71">
-        <v>-2.3194</v>
+        <v>-2.182</v>
       </c>
       <c r="F71">
-        <v>9.480600000000001</v>
+        <v>9.618</v>
       </c>
       <c r="G71">
         <v>2.62</v>
@@ -7097,28 +7097,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M71">
-        <v>0.5147965800000001</v>
+        <v>0.5222574</v>
       </c>
       <c r="N71">
-        <v>3.274387093469388</v>
+        <v>3.266926273469388</v>
       </c>
       <c r="O71">
-        <v>0.818596773367347</v>
+        <v>0.8167315683673471</v>
       </c>
       <c r="P71">
-        <v>2.455790320102041</v>
+        <v>2.450194705102041</v>
       </c>
       <c r="Q71">
-        <v>3.625790320102041</v>
+        <v>3.620194705102041</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1908599849362228</v>
+        <v>0.1952424618225135</v>
       </c>
       <c r="T71">
-        <v>1.996805293948243</v>
+        <v>2.057131737874171</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.360545544940076</v>
+        <v>7.255394894298076</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08708023854675404</v>
+        <v>0.08689363176327904</v>
       </c>
       <c r="C72">
-        <v>4.888569051479317</v>
+        <v>4.762667041055536</v>
       </c>
       <c r="D72">
-        <v>11.88656905147932</v>
+        <v>11.89806704105554</v>
       </c>
       <c r="E72">
-        <v>-2.182</v>
+        <v>-2.044599999999999</v>
       </c>
       <c r="F72">
-        <v>9.618</v>
+        <v>9.755400000000002</v>
       </c>
       <c r="G72">
         <v>2.62</v>
@@ -7179,28 +7179,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M72">
-        <v>0.5222574</v>
+        <v>0.5297182200000001</v>
       </c>
       <c r="N72">
-        <v>3.266926273469388</v>
+        <v>3.259465453469388</v>
       </c>
       <c r="O72">
-        <v>0.8167315683673471</v>
+        <v>0.814866363367347</v>
       </c>
       <c r="P72">
-        <v>2.450194705102041</v>
+        <v>2.444599090102041</v>
       </c>
       <c r="Q72">
-        <v>3.620194705102041</v>
+        <v>3.614599090102041</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1952424618225135</v>
+        <v>0.1999271784940657</v>
       </c>
       <c r="T72">
-        <v>2.057131737874171</v>
+        <v>2.121618626208785</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>7.255394894298076</v>
+        <v>7.153206233815003</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08689363176327905</v>
+        <v>0.08670702497980402</v>
       </c>
       <c r="C73">
-        <v>4.762667041055538</v>
+        <v>4.636787296395665</v>
       </c>
       <c r="D73">
-        <v>11.89806704105554</v>
+        <v>11.90958729639567</v>
       </c>
       <c r="E73">
-        <v>-2.044600000000001</v>
+        <v>-1.907200000000001</v>
       </c>
       <c r="F73">
-        <v>9.7554</v>
+        <v>9.892799999999999</v>
       </c>
       <c r="G73">
         <v>2.62</v>
@@ -7261,28 +7261,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M73">
-        <v>0.52971822</v>
+        <v>0.5371790399999999</v>
       </c>
       <c r="N73">
-        <v>3.259465453469388</v>
+        <v>3.252004633469388</v>
       </c>
       <c r="O73">
-        <v>0.8148663633673471</v>
+        <v>0.8130011583673471</v>
       </c>
       <c r="P73">
-        <v>2.444599090102041</v>
+        <v>2.439003475102041</v>
       </c>
       <c r="Q73">
-        <v>3.614599090102041</v>
+        <v>3.609003475102041</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1999271784940657</v>
+        <v>0.2049465177850144</v>
       </c>
       <c r="T73">
-        <v>2.121618626208785</v>
+        <v>2.190711720853013</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.153206233815005</v>
+        <v>7.053856147234242</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08670702497980402</v>
+        <v>0.08652041819632902</v>
       </c>
       <c r="C74">
-        <v>4.636787296395665</v>
+        <v>4.510929882238582</v>
       </c>
       <c r="D74">
-        <v>11.90958729639567</v>
+        <v>11.92112988223858</v>
       </c>
       <c r="E74">
-        <v>-1.907200000000001</v>
+        <v>-1.7698</v>
       </c>
       <c r="F74">
-        <v>9.892799999999999</v>
+        <v>10.0302</v>
       </c>
       <c r="G74">
         <v>2.62</v>
@@ -7343,28 +7343,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M74">
-        <v>0.5371790399999999</v>
+        <v>0.5446398600000001</v>
       </c>
       <c r="N74">
-        <v>3.252004633469388</v>
+        <v>3.244543813469388</v>
       </c>
       <c r="O74">
-        <v>0.8130011583673471</v>
+        <v>0.811135953367347</v>
       </c>
       <c r="P74">
-        <v>2.439003475102041</v>
+        <v>2.433407860102041</v>
       </c>
       <c r="Q74">
-        <v>3.609003475102041</v>
+        <v>3.603407860102041</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2049465177850144</v>
+        <v>0.2103376599864037</v>
       </c>
       <c r="T74">
-        <v>2.190711720853013</v>
+        <v>2.264922822507926</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.053856147234242</v>
+        <v>6.95722798083377</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08652041819632902</v>
+        <v>0.08633381141285398</v>
       </c>
       <c r="C75">
-        <v>4.510929882238582</v>
+        <v>4.385094863574405</v>
       </c>
       <c r="D75">
-        <v>11.92112988223858</v>
+        <v>11.93269486357441</v>
       </c>
       <c r="E75">
-        <v>-1.7698</v>
+        <v>-1.632400000000001</v>
       </c>
       <c r="F75">
-        <v>10.0302</v>
+        <v>10.1676</v>
       </c>
       <c r="G75">
         <v>2.62</v>
@@ -7425,28 +7425,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M75">
-        <v>0.5446398600000001</v>
+        <v>0.55210068</v>
       </c>
       <c r="N75">
-        <v>3.244543813469388</v>
+        <v>3.237082993469388</v>
       </c>
       <c r="O75">
-        <v>0.811135953367347</v>
+        <v>0.809270748367347</v>
       </c>
       <c r="P75">
-        <v>2.433407860102041</v>
+        <v>2.427812245102041</v>
       </c>
       <c r="Q75">
-        <v>3.603407860102041</v>
+        <v>3.597812245102041</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2103376599864037</v>
+        <v>0.2161435054340538</v>
       </c>
       <c r="T75">
-        <v>2.264922822507926</v>
+        <v>2.344842470443985</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.95722798083377</v>
+        <v>6.86321138649818</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08633381141285398</v>
+        <v>0.08614720462937898</v>
       </c>
       <c r="C76">
-        <v>4.385094863574405</v>
+        <v>4.25928230564568</v>
       </c>
       <c r="D76">
-        <v>11.93269486357441</v>
+        <v>11.94428230564568</v>
       </c>
       <c r="E76">
-        <v>-1.632400000000001</v>
+        <v>-1.495000000000001</v>
       </c>
       <c r="F76">
-        <v>10.1676</v>
+        <v>10.305</v>
       </c>
       <c r="G76">
         <v>2.62</v>
@@ -7507,28 +7507,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M76">
-        <v>0.55210068</v>
+        <v>0.5595615</v>
       </c>
       <c r="N76">
-        <v>3.237082993469388</v>
+        <v>3.229622173469388</v>
       </c>
       <c r="O76">
-        <v>0.809270748367347</v>
+        <v>0.807405543367347</v>
       </c>
       <c r="P76">
-        <v>2.427812245102041</v>
+        <v>2.422216630102041</v>
       </c>
       <c r="Q76">
-        <v>3.597812245102041</v>
+        <v>3.592216630102041</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2161435054340538</v>
+        <v>0.2224138185175159</v>
       </c>
       <c r="T76">
-        <v>2.344842470443985</v>
+        <v>2.431155690214929</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.86321138649818</v>
+        <v>6.771701901344871</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08614720462937898</v>
+        <v>0.08596059784590397</v>
       </c>
       <c r="C77">
-        <v>4.25928230564568</v>
+        <v>4.133492273948621</v>
       </c>
       <c r="D77">
-        <v>11.94428230564568</v>
+        <v>11.95589227394862</v>
       </c>
       <c r="E77">
-        <v>-1.495000000000001</v>
+        <v>-1.3576</v>
       </c>
       <c r="F77">
-        <v>10.305</v>
+        <v>10.4424</v>
       </c>
       <c r="G77">
         <v>2.62</v>
@@ -7589,28 +7589,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M77">
-        <v>0.5595615</v>
+        <v>0.5670223200000001</v>
       </c>
       <c r="N77">
-        <v>3.229622173469388</v>
+        <v>3.222161353469388</v>
       </c>
       <c r="O77">
-        <v>0.807405543367347</v>
+        <v>0.8055403383673471</v>
       </c>
       <c r="P77">
-        <v>2.422216630102041</v>
+        <v>2.416621015102041</v>
       </c>
       <c r="Q77">
-        <v>3.592216630102041</v>
+        <v>3.586621015102041</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2224138185175159</v>
+        <v>0.2292066576912666</v>
       </c>
       <c r="T77">
-        <v>2.431155690214929</v>
+        <v>2.524661678300119</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.771701901344871</v>
+        <v>6.682600560537701</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08596059784590397</v>
+        <v>0.08577399106242894</v>
       </c>
       <c r="C78">
-        <v>4.133492273948621</v>
+        <v>4.007724834234347</v>
       </c>
       <c r="D78">
-        <v>11.95589227394862</v>
+        <v>11.96752483423435</v>
       </c>
       <c r="E78">
-        <v>-1.3576</v>
+        <v>-1.2202</v>
       </c>
       <c r="F78">
-        <v>10.4424</v>
+        <v>10.5798</v>
       </c>
       <c r="G78">
         <v>2.62</v>
@@ -7671,28 +7671,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M78">
-        <v>0.5670223200000001</v>
+        <v>0.57448314</v>
       </c>
       <c r="N78">
-        <v>3.222161353469388</v>
+        <v>3.214700533469388</v>
       </c>
       <c r="O78">
-        <v>0.8055403383673471</v>
+        <v>0.8036751333673471</v>
       </c>
       <c r="P78">
-        <v>2.416621015102041</v>
+        <v>2.411025400102041</v>
       </c>
       <c r="Q78">
-        <v>3.586621015102041</v>
+        <v>3.581025400102041</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2292066576912666</v>
+        <v>0.2365901785322998</v>
       </c>
       <c r="T78">
-        <v>2.524661678300119</v>
+        <v>2.626298621870977</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.682600560537701</v>
+        <v>6.595813540270979</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08577399106242894</v>
+        <v>0.08558738427895395</v>
       </c>
       <c r="C79">
-        <v>4.007724834234347</v>
+        <v>3.88198005251011</v>
       </c>
       <c r="D79">
-        <v>11.96752483423435</v>
+        <v>11.97918005251011</v>
       </c>
       <c r="E79">
-        <v>-1.2202</v>
+        <v>-1.082800000000001</v>
       </c>
       <c r="F79">
-        <v>10.5798</v>
+        <v>10.7172</v>
       </c>
       <c r="G79">
         <v>2.62</v>
@@ -7753,28 +7753,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M79">
-        <v>0.57448314</v>
+        <v>0.58194396</v>
       </c>
       <c r="N79">
-        <v>3.214700533469388</v>
+        <v>3.207239713469388</v>
       </c>
       <c r="O79">
-        <v>0.8036751333673471</v>
+        <v>0.801809928367347</v>
       </c>
       <c r="P79">
-        <v>2.411025400102041</v>
+        <v>2.405429785102041</v>
       </c>
       <c r="Q79">
-        <v>3.581025400102041</v>
+        <v>3.575429785102041</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2365901785322998</v>
+        <v>0.2446449285406998</v>
       </c>
       <c r="T79">
-        <v>2.626298621870977</v>
+        <v>2.737175287584641</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.595813540270979</v>
+        <v>6.511251828216222</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08558738427895395</v>
+        <v>0.08540077749547893</v>
       </c>
       <c r="C80">
-        <v>3.88198005251011</v>
+        <v>3.756257995040553</v>
       </c>
       <c r="D80">
-        <v>11.97918005251011</v>
+        <v>11.99085799504055</v>
       </c>
       <c r="E80">
-        <v>-1.082800000000001</v>
+        <v>-0.9453999999999994</v>
       </c>
       <c r="F80">
-        <v>10.7172</v>
+        <v>10.8546</v>
       </c>
       <c r="G80">
         <v>2.62</v>
@@ -7835,28 +7835,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M80">
-        <v>0.58194396</v>
+        <v>0.5894047800000001</v>
       </c>
       <c r="N80">
-        <v>3.207239713469388</v>
+        <v>3.199778893469388</v>
       </c>
       <c r="O80">
-        <v>0.801809928367347</v>
+        <v>0.799944723367347</v>
       </c>
       <c r="P80">
-        <v>2.405429785102041</v>
+        <v>2.399834170102041</v>
       </c>
       <c r="Q80">
-        <v>3.575429785102041</v>
+        <v>3.569834170102041</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2446449285406998</v>
+        <v>0.2534667975975188</v>
       </c>
       <c r="T80">
-        <v>2.737175287584641</v>
+        <v>2.858611635747225</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.511251828216222</v>
+        <v>6.428830918998295</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08540077749547893</v>
+        <v>0.08521417071200391</v>
       </c>
       <c r="C81">
-        <v>3.756257995040553</v>
+        <v>3.630558728348973</v>
       </c>
       <c r="D81">
-        <v>11.99085799504055</v>
+        <v>12.00255872834897</v>
       </c>
       <c r="E81">
-        <v>-0.9453999999999994</v>
+        <v>-0.8079999999999998</v>
       </c>
       <c r="F81">
-        <v>10.8546</v>
+        <v>10.992</v>
       </c>
       <c r="G81">
         <v>2.62</v>
@@ -7917,28 +7917,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M81">
-        <v>0.5894047800000001</v>
+        <v>0.5968656000000001</v>
       </c>
       <c r="N81">
-        <v>3.199778893469388</v>
+        <v>3.192318073469388</v>
       </c>
       <c r="O81">
-        <v>0.799944723367347</v>
+        <v>0.798079518367347</v>
       </c>
       <c r="P81">
-        <v>2.399834170102041</v>
+        <v>2.394238555102041</v>
       </c>
       <c r="Q81">
-        <v>3.569834170102041</v>
+        <v>3.564238555102041</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2534667975975188</v>
+        <v>0.2631708535600196</v>
       </c>
       <c r="T81">
-        <v>2.858611635747225</v>
+        <v>2.992191618726067</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.428830918998295</v>
+        <v>6.348470532510816</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08521417071200391</v>
+        <v>0.08502756392852891</v>
       </c>
       <c r="C82">
-        <v>3.630558728348973</v>
+        <v>3.504882319218567</v>
       </c>
       <c r="D82">
-        <v>12.00255872834897</v>
+        <v>12.01428231921857</v>
       </c>
       <c r="E82">
-        <v>-0.8079999999999998</v>
+        <v>-0.6706000000000003</v>
       </c>
       <c r="F82">
-        <v>10.992</v>
+        <v>11.1294</v>
       </c>
       <c r="G82">
         <v>2.62</v>
@@ -7999,28 +7999,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M82">
-        <v>0.5968656000000001</v>
+        <v>0.60432642</v>
       </c>
       <c r="N82">
-        <v>3.192318073469388</v>
+        <v>3.184857253469388</v>
       </c>
       <c r="O82">
-        <v>0.798079518367347</v>
+        <v>0.796214313367347</v>
       </c>
       <c r="P82">
-        <v>2.394238555102041</v>
+        <v>2.388642940102041</v>
       </c>
       <c r="Q82">
-        <v>3.564238555102041</v>
+        <v>3.558642940102041</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2631708535600196</v>
+        <v>0.2738963890975206</v>
       </c>
       <c r="T82">
-        <v>2.992191618726067</v>
+        <v>3.139832652544788</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.348470532510816</v>
+        <v>6.270094353097103</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08502756392852891</v>
+        <v>0.08484095714505388</v>
       </c>
       <c r="C83">
-        <v>3.504882319218567</v>
+        <v>3.379228834693711</v>
       </c>
       <c r="D83">
-        <v>12.01428231921857</v>
+        <v>12.02602883469371</v>
       </c>
       <c r="E83">
-        <v>-0.6706000000000003</v>
+        <v>-0.533199999999999</v>
       </c>
       <c r="F83">
-        <v>11.1294</v>
+        <v>11.2668</v>
       </c>
       <c r="G83">
         <v>2.62</v>
@@ -8081,28 +8081,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M83">
-        <v>0.60432642</v>
+        <v>0.6117872400000001</v>
       </c>
       <c r="N83">
-        <v>3.184857253469388</v>
+        <v>3.177396433469388</v>
       </c>
       <c r="O83">
-        <v>0.796214313367347</v>
+        <v>0.7943491083673471</v>
       </c>
       <c r="P83">
-        <v>2.388642940102041</v>
+        <v>2.383047325102041</v>
       </c>
       <c r="Q83">
-        <v>3.558642940102041</v>
+        <v>3.553047325102041</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2738963890975206</v>
+        <v>0.285813650805855</v>
       </c>
       <c r="T83">
-        <v>3.139832652544788</v>
+        <v>3.3038782456767</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.270094353097103</v>
+        <v>6.19362978781543</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08484095714505388</v>
+        <v>0.0846543503615789</v>
       </c>
       <c r="C84">
-        <v>3.379228834693711</v>
+        <v>3.253598342081238</v>
       </c>
       <c r="D84">
-        <v>12.02602883469371</v>
+        <v>12.03779834208124</v>
       </c>
       <c r="E84">
-        <v>-0.533199999999999</v>
+        <v>-0.3957999999999995</v>
       </c>
       <c r="F84">
-        <v>11.2668</v>
+        <v>11.4042</v>
       </c>
       <c r="G84">
         <v>2.62</v>
@@ -8163,28 +8163,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M84">
-        <v>0.6117872400000001</v>
+        <v>0.6192480600000001</v>
       </c>
       <c r="N84">
-        <v>3.177396433469388</v>
+        <v>3.169935613469388</v>
       </c>
       <c r="O84">
-        <v>0.7943491083673471</v>
+        <v>0.792483903367347</v>
       </c>
       <c r="P84">
-        <v>2.383047325102041</v>
+        <v>2.377451710102041</v>
       </c>
       <c r="Q84">
-        <v>3.553047325102041</v>
+        <v>3.547451710102041</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.285813650805855</v>
+        <v>0.2991329433034053</v>
       </c>
       <c r="T84">
-        <v>3.3038782456767</v>
+        <v>3.487223320353543</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.19362978781543</v>
+        <v>6.119007742179099</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0846543503615789</v>
+        <v>0.08509774357810387</v>
       </c>
       <c r="C85">
-        <v>3.253598342081238</v>
+        <v>3.088270589372391</v>
       </c>
       <c r="D85">
-        <v>12.03779834208124</v>
+        <v>12.00987058937239</v>
       </c>
       <c r="E85">
-        <v>-0.3957999999999995</v>
+        <v>-0.2584</v>
       </c>
       <c r="F85">
-        <v>11.4042</v>
+        <v>11.5416</v>
       </c>
       <c r="G85">
         <v>2.62</v>
@@ -8245,45 +8245,45 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M85">
-        <v>0.6192480600000001</v>
+        <v>0.6382504800000001</v>
       </c>
       <c r="N85">
-        <v>3.169935613469388</v>
+        <v>3.150933193469388</v>
       </c>
       <c r="O85">
-        <v>0.792483903367347</v>
+        <v>0.7877332983673471</v>
       </c>
       <c r="P85">
-        <v>2.377451710102041</v>
+        <v>2.363199895102041</v>
       </c>
       <c r="Q85">
-        <v>3.547451710102041</v>
+        <v>3.533199895102041</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2991329433034053</v>
+        <v>0.3141171473631494</v>
       </c>
       <c r="T85">
-        <v>3.487223320353543</v>
+        <v>3.693486529364991</v>
       </c>
       <c r="U85">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V85">
         <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y85">
-        <v>6.119007742179099</v>
+        <v>5.936828552748426</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08509774357810387</v>
+        <v>0.08491863679462888</v>
       </c>
       <c r="C86">
-        <v>3.088270589372392</v>
+        <v>2.962136270043837</v>
       </c>
       <c r="D86">
-        <v>12.00987058937239</v>
+        <v>12.02113627004384</v>
       </c>
       <c r="E86">
-        <v>-0.2584000000000017</v>
+        <v>-0.1210000000000004</v>
       </c>
       <c r="F86">
-        <v>11.5416</v>
+        <v>11.679</v>
       </c>
       <c r="G86">
         <v>2.62</v>
@@ -8327,28 +8327,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M86">
-        <v>0.63825048</v>
+        <v>0.6458487000000001</v>
       </c>
       <c r="N86">
-        <v>3.150933193469388</v>
+        <v>3.143334973469388</v>
       </c>
       <c r="O86">
-        <v>0.7877332983673471</v>
+        <v>0.785833743367347</v>
       </c>
       <c r="P86">
-        <v>2.363199895102041</v>
+        <v>2.357501230102041</v>
       </c>
       <c r="Q86">
-        <v>3.533199895102041</v>
+        <v>3.527501230102041</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3141171473631492</v>
+        <v>0.3310992452975258</v>
       </c>
       <c r="T86">
-        <v>3.693486529364988</v>
+        <v>3.927251499577963</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.936828552748427</v>
+        <v>5.866983510951385</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08491863679462888</v>
+        <v>0.08473953001115385</v>
       </c>
       <c r="C87">
-        <v>2.962136270043837</v>
+        <v>2.836023105768222</v>
       </c>
       <c r="D87">
-        <v>12.02113627004384</v>
+        <v>12.03242310576822</v>
       </c>
       <c r="E87">
-        <v>-0.1210000000000004</v>
+        <v>0.01639999999999908</v>
       </c>
       <c r="F87">
-        <v>11.679</v>
+        <v>11.8164</v>
       </c>
       <c r="G87">
         <v>2.62</v>
@@ -8409,28 +8409,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M87">
-        <v>0.6458487000000001</v>
+        <v>0.65344692</v>
       </c>
       <c r="N87">
-        <v>3.143334973469388</v>
+        <v>3.135736753469388</v>
       </c>
       <c r="O87">
-        <v>0.785833743367347</v>
+        <v>0.7839341883673471</v>
       </c>
       <c r="P87">
-        <v>2.357501230102041</v>
+        <v>2.351802565102041</v>
       </c>
       <c r="Q87">
-        <v>3.527501230102041</v>
+        <v>3.521802565102041</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3310992452975258</v>
+        <v>0.3505073572225275</v>
       </c>
       <c r="T87">
-        <v>3.927251499577963</v>
+        <v>4.194411465535647</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.866983510951385</v>
+        <v>5.79876277245195</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08473953001115385</v>
+        <v>0.08456042322767884</v>
       </c>
       <c r="C88">
-        <v>2.836023105768222</v>
+        <v>2.709931156189986</v>
       </c>
       <c r="D88">
-        <v>12.03242310576822</v>
+        <v>12.04373115618998</v>
       </c>
       <c r="E88">
-        <v>0.01639999999999908</v>
+        <v>0.1537999999999986</v>
       </c>
       <c r="F88">
-        <v>11.8164</v>
+        <v>11.9538</v>
       </c>
       <c r="G88">
         <v>2.62</v>
@@ -8491,28 +8491,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M88">
-        <v>0.65344692</v>
+        <v>0.66104514</v>
       </c>
       <c r="N88">
-        <v>3.135736753469388</v>
+        <v>3.128138533469388</v>
       </c>
       <c r="O88">
-        <v>0.7839341883673471</v>
+        <v>0.782034633367347</v>
       </c>
       <c r="P88">
-        <v>2.351802565102041</v>
+        <v>2.346103900102041</v>
       </c>
       <c r="Q88">
-        <v>3.521802565102041</v>
+        <v>3.516103900102041</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3505073572225275</v>
+        <v>0.3729013325206064</v>
       </c>
       <c r="T88">
-        <v>4.194411465535647</v>
+        <v>4.502672964717591</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.79876277245195</v>
+        <v>5.732110326791584</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08456042322767884</v>
+        <v>0.08438131644420382</v>
       </c>
       <c r="C89">
-        <v>2.709931156189986</v>
+        <v>2.583860481178</v>
       </c>
       <c r="D89">
-        <v>12.04373115618998</v>
+        <v>12.055060481178</v>
       </c>
       <c r="E89">
-        <v>0.1537999999999986</v>
+        <v>0.2911999999999999</v>
       </c>
       <c r="F89">
-        <v>11.9538</v>
+        <v>12.0912</v>
       </c>
       <c r="G89">
         <v>2.62</v>
@@ -8573,28 +8573,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M89">
-        <v>0.66104514</v>
+        <v>0.66864336</v>
       </c>
       <c r="N89">
-        <v>3.128138533469388</v>
+        <v>3.120540313469388</v>
       </c>
       <c r="O89">
-        <v>0.782034633367347</v>
+        <v>0.7801350783673471</v>
       </c>
       <c r="P89">
-        <v>2.346103900102041</v>
+        <v>2.340405235102041</v>
       </c>
       <c r="Q89">
-        <v>3.516103900102041</v>
+        <v>3.510405235102041</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3729013325206064</v>
+        <v>0.3990276370350319</v>
       </c>
       <c r="T89">
-        <v>4.502672964717591</v>
+        <v>4.862311380429858</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.732110326791584</v>
+        <v>5.666972709441679</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08438131644420382</v>
+        <v>0.08420220966072881</v>
       </c>
       <c r="C90">
-        <v>2.583860481178</v>
+        <v>2.457811140826628</v>
       </c>
       <c r="D90">
-        <v>12.055060481178</v>
+        <v>12.06641114082663</v>
       </c>
       <c r="E90">
-        <v>0.2911999999999999</v>
+        <v>0.4285999999999994</v>
       </c>
       <c r="F90">
-        <v>12.0912</v>
+        <v>12.2286</v>
       </c>
       <c r="G90">
         <v>2.62</v>
@@ -8655,28 +8655,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M90">
-        <v>0.66864336</v>
+        <v>0.67624158</v>
       </c>
       <c r="N90">
-        <v>3.120540313469388</v>
+        <v>3.112942093469388</v>
       </c>
       <c r="O90">
-        <v>0.7801350783673471</v>
+        <v>0.778235523367347</v>
       </c>
       <c r="P90">
-        <v>2.340405235102041</v>
+        <v>2.334706570102041</v>
       </c>
       <c r="Q90">
-        <v>3.510405235102041</v>
+        <v>3.504706570102041</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3990276370350319</v>
+        <v>0.4299041787338983</v>
       </c>
       <c r="T90">
-        <v>4.862311380429858</v>
+        <v>5.287338598998902</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.666972709441679</v>
+        <v>5.603298858773795</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08420220966072881</v>
+        <v>0.0840231028772538</v>
       </c>
       <c r="C91">
-        <v>2.457811140826628</v>
+        <v>2.331783195456762</v>
       </c>
       <c r="D91">
-        <v>12.06641114082663</v>
+        <v>12.07778319545676</v>
       </c>
       <c r="E91">
-        <v>0.4285999999999994</v>
+        <v>0.5659999999999989</v>
       </c>
       <c r="F91">
-        <v>12.2286</v>
+        <v>12.366</v>
       </c>
       <c r="G91">
         <v>2.62</v>
@@ -8737,28 +8737,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M91">
-        <v>0.67624158</v>
+        <v>0.6838398</v>
       </c>
       <c r="N91">
-        <v>3.112942093469388</v>
+        <v>3.105343873469388</v>
       </c>
       <c r="O91">
-        <v>0.778235523367347</v>
+        <v>0.7763359683673471</v>
       </c>
       <c r="P91">
-        <v>2.334706570102041</v>
+        <v>2.329007905102041</v>
       </c>
       <c r="Q91">
-        <v>3.504706570102041</v>
+        <v>3.499007905102041</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4299041787338983</v>
+        <v>0.4669560287725381</v>
       </c>
       <c r="T91">
-        <v>5.287338598998902</v>
+        <v>5.797371261281756</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.603298858773795</v>
+        <v>5.541039982565198</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0840231028772538</v>
+        <v>0.08384399609377878</v>
       </c>
       <c r="C92">
-        <v>2.331783195456762</v>
+        <v>2.205776705616914</v>
       </c>
       <c r="D92">
-        <v>12.07778319545676</v>
+        <v>12.08917670561691</v>
       </c>
       <c r="E92">
-        <v>0.5659999999999989</v>
+        <v>0.7034000000000002</v>
       </c>
       <c r="F92">
-        <v>12.366</v>
+        <v>12.5034</v>
       </c>
       <c r="G92">
         <v>2.62</v>
@@ -8819,28 +8819,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M92">
-        <v>0.6838398</v>
+        <v>0.6914380200000001</v>
       </c>
       <c r="N92">
-        <v>3.105343873469388</v>
+        <v>3.097745653469388</v>
       </c>
       <c r="O92">
-        <v>0.7763359683673471</v>
+        <v>0.774436413367347</v>
       </c>
       <c r="P92">
-        <v>2.329007905102041</v>
+        <v>2.323309240102041</v>
       </c>
       <c r="Q92">
-        <v>3.499007905102041</v>
+        <v>3.493309240102041</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4669560287725381</v>
+        <v>0.5122416232642089</v>
       </c>
       <c r="T92">
-        <v>5.797371261281756</v>
+        <v>6.420744515183021</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.541039982565198</v>
+        <v>5.480149433306239</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08384399609377878</v>
+        <v>0.08366488931030377</v>
       </c>
       <c r="C93">
-        <v>2.205776705616914</v>
+        <v>2.07979173208429</v>
       </c>
       <c r="D93">
-        <v>12.08917670561691</v>
+        <v>12.10059173208429</v>
       </c>
       <c r="E93">
-        <v>0.7034000000000002</v>
+        <v>0.8407999999999998</v>
       </c>
       <c r="F93">
-        <v>12.5034</v>
+        <v>12.6408</v>
       </c>
       <c r="G93">
         <v>2.62</v>
@@ -8901,28 +8901,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M93">
-        <v>0.6914380200000001</v>
+        <v>0.6990362400000001</v>
       </c>
       <c r="N93">
-        <v>3.097745653469388</v>
+        <v>3.090147433469388</v>
       </c>
       <c r="O93">
-        <v>0.774436413367347</v>
+        <v>0.7725368583673471</v>
       </c>
       <c r="P93">
-        <v>2.323309240102041</v>
+        <v>2.317610575102041</v>
       </c>
       <c r="Q93">
-        <v>3.493309240102041</v>
+        <v>3.487610575102041</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5122416232642089</v>
+        <v>0.5688486163787975</v>
       </c>
       <c r="T93">
-        <v>6.420744515183021</v>
+        <v>7.199961082559603</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.480149433306239</v>
+        <v>5.420582591639866</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08366488931030377</v>
+        <v>0.08348578252682876</v>
       </c>
       <c r="C94">
-        <v>2.07979173208429</v>
+        <v>1.953828335865859</v>
       </c>
       <c r="D94">
-        <v>12.10059173208429</v>
+        <v>12.11202833586586</v>
       </c>
       <c r="E94">
-        <v>0.8407999999999998</v>
+        <v>0.9781999999999993</v>
       </c>
       <c r="F94">
-        <v>12.6408</v>
+        <v>12.7782</v>
       </c>
       <c r="G94">
         <v>2.62</v>
@@ -8983,28 +8983,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M94">
-        <v>0.6990362400000001</v>
+        <v>0.7066344600000001</v>
       </c>
       <c r="N94">
-        <v>3.090147433469388</v>
+        <v>3.082549213469388</v>
       </c>
       <c r="O94">
-        <v>0.7725368583673471</v>
+        <v>0.770637303367347</v>
       </c>
       <c r="P94">
-        <v>2.317610575102041</v>
+        <v>2.311911910102041</v>
       </c>
       <c r="Q94">
-        <v>3.487610575102041</v>
+        <v>3.481911910102041</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5688486163787975</v>
+        <v>0.6416290360975542</v>
       </c>
       <c r="T94">
-        <v>7.199961082559603</v>
+        <v>8.201810954900921</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.420582591639866</v>
+        <v>5.362296757321158</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08348578252682876</v>
+        <v>0.08330667574335374</v>
       </c>
       <c r="C95">
-        <v>1.953828335865859</v>
+        <v>1.82788657819945</v>
       </c>
       <c r="D95">
-        <v>12.11202833586586</v>
+        <v>12.12348657819945</v>
       </c>
       <c r="E95">
-        <v>0.9781999999999993</v>
+        <v>1.115600000000001</v>
       </c>
       <c r="F95">
-        <v>12.7782</v>
+        <v>12.9156</v>
       </c>
       <c r="G95">
         <v>2.62</v>
@@ -9065,28 +9065,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M95">
-        <v>0.7066344600000001</v>
+        <v>0.7142326800000001</v>
       </c>
       <c r="N95">
-        <v>3.082549213469388</v>
+        <v>3.074950993469388</v>
       </c>
       <c r="O95">
-        <v>0.770637303367347</v>
+        <v>0.768737748367347</v>
       </c>
       <c r="P95">
-        <v>2.311911910102041</v>
+        <v>2.306213245102041</v>
       </c>
       <c r="Q95">
-        <v>3.481911910102041</v>
+        <v>3.476213245102041</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6416290360975542</v>
+        <v>0.738669595722563</v>
       </c>
       <c r="T95">
-        <v>8.201810954900921</v>
+        <v>9.537610784689345</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.362296757321158</v>
+        <v>5.30525104713689</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08330667574335374</v>
+        <v>0.08312756895987874</v>
       </c>
       <c r="C96">
-        <v>1.82788657819945</v>
+        <v>1.701966520554834</v>
       </c>
       <c r="D96">
-        <v>12.12348657819945</v>
+        <v>12.13496652055483</v>
       </c>
       <c r="E96">
-        <v>1.115600000000001</v>
+        <v>1.253</v>
       </c>
       <c r="F96">
-        <v>12.9156</v>
+        <v>13.053</v>
       </c>
       <c r="G96">
         <v>2.62</v>
@@ -9147,28 +9147,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M96">
-        <v>0.7142326800000001</v>
+        <v>0.7218309000000001</v>
       </c>
       <c r="N96">
-        <v>3.074950993469388</v>
+        <v>3.067352773469388</v>
       </c>
       <c r="O96">
-        <v>0.768737748367347</v>
+        <v>0.766838193367347</v>
       </c>
       <c r="P96">
-        <v>2.306213245102041</v>
+        <v>2.300514580102041</v>
       </c>
       <c r="Q96">
-        <v>3.476213245102041</v>
+        <v>3.470514580102041</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.738669595722563</v>
+        <v>0.8745263791975759</v>
       </c>
       <c r="T96">
-        <v>9.537610784689345</v>
+        <v>11.40773054639315</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.30525104713689</v>
+        <v>5.249406299272292</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08312756895987874</v>
+        <v>0.08294846217640373</v>
       </c>
       <c r="C97">
-        <v>1.701966520554834</v>
+        <v>1.576068224634833</v>
       </c>
       <c r="D97">
-        <v>12.13496652055483</v>
+        <v>12.14646822463484</v>
       </c>
       <c r="E97">
-        <v>1.253</v>
+        <v>1.390400000000001</v>
       </c>
       <c r="F97">
-        <v>13.053</v>
+        <v>13.1904</v>
       </c>
       <c r="G97">
         <v>2.62</v>
@@ -9229,28 +9229,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M97">
-        <v>0.7218309000000001</v>
+        <v>0.7294291200000002</v>
       </c>
       <c r="N97">
-        <v>3.067352773469388</v>
+        <v>3.059754553469388</v>
       </c>
       <c r="O97">
-        <v>0.766838193367347</v>
+        <v>0.764938638367347</v>
       </c>
       <c r="P97">
-        <v>2.300514580102041</v>
+        <v>2.294815915102041</v>
       </c>
       <c r="Q97">
-        <v>3.470514580102041</v>
+        <v>3.464815915102041</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8745263791975759</v>
+        <v>1.078311554410095</v>
       </c>
       <c r="T97">
-        <v>11.40773054639315</v>
+        <v>14.21291018894884</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.249406299272292</v>
+        <v>5.194724983654871</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08294846217640374</v>
+        <v>0.08276935539292871</v>
       </c>
       <c r="C98">
-        <v>1.576068224634835</v>
+        <v>1.45019175237643</v>
       </c>
       <c r="D98">
-        <v>12.14646822463484</v>
+        <v>12.15799175237643</v>
       </c>
       <c r="E98">
-        <v>1.3904</v>
+        <v>1.527799999999999</v>
       </c>
       <c r="F98">
-        <v>13.1904</v>
+        <v>13.3278</v>
       </c>
       <c r="G98">
         <v>2.62</v>
@@ -9311,28 +9311,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M98">
-        <v>0.72942912</v>
+        <v>0.73702734</v>
       </c>
       <c r="N98">
-        <v>3.059754553469388</v>
+        <v>3.052156333469388</v>
       </c>
       <c r="O98">
-        <v>0.7649386383673471</v>
+        <v>0.763039083367347</v>
       </c>
       <c r="P98">
-        <v>2.294815915102041</v>
+        <v>2.289117250102041</v>
       </c>
       <c r="Q98">
-        <v>3.464815915102041</v>
+        <v>3.459117250102041</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.078311554410093</v>
+        <v>1.417953513097623</v>
       </c>
       <c r="T98">
-        <v>14.21291018894881</v>
+        <v>18.88820959320828</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.194724983654873</v>
+        <v>5.141171117843998</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08276935539292871</v>
+        <v>0.0825902486094537</v>
       </c>
       <c r="C99">
-        <v>1.45019175237643</v>
+        <v>1.324337165951853</v>
       </c>
       <c r="D99">
-        <v>12.15799175237643</v>
+        <v>12.16953716595185</v>
       </c>
       <c r="E99">
-        <v>1.527799999999999</v>
+        <v>1.665199999999999</v>
       </c>
       <c r="F99">
-        <v>13.3278</v>
+        <v>13.4652</v>
       </c>
       <c r="G99">
         <v>2.62</v>
@@ -9393,28 +9393,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M99">
-        <v>0.73702734</v>
+        <v>0.74462556</v>
       </c>
       <c r="N99">
-        <v>3.052156333469388</v>
+        <v>3.044558113469388</v>
       </c>
       <c r="O99">
-        <v>0.763039083367347</v>
+        <v>0.761139528367347</v>
       </c>
       <c r="P99">
-        <v>2.289117250102041</v>
+        <v>2.283418585102041</v>
       </c>
       <c r="Q99">
-        <v>3.459117250102041</v>
+        <v>3.453418585102041</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.417953513097623</v>
+        <v>2.097237430472684</v>
       </c>
       <c r="T99">
-        <v>18.88820959320828</v>
+        <v>28.23880840172723</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.141171117843998</v>
+        <v>5.088710188070079</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0825902486094537</v>
+        <v>0.0824111418259787</v>
       </c>
       <c r="C100">
-        <v>1.324337165951853</v>
+        <v>1.198504527769741</v>
       </c>
       <c r="D100">
-        <v>12.16953716595185</v>
+        <v>12.18110452776974</v>
       </c>
       <c r="E100">
-        <v>1.665199999999999</v>
+        <v>1.8026</v>
       </c>
       <c r="F100">
-        <v>13.4652</v>
+        <v>13.6026</v>
       </c>
       <c r="G100">
         <v>2.62</v>
@@ -9475,28 +9475,28 @@
         <v>3.789183673469388</v>
       </c>
       <c r="M100">
-        <v>0.74462556</v>
+        <v>0.7522237800000001</v>
       </c>
       <c r="N100">
-        <v>3.044558113469388</v>
+        <v>3.036959893469388</v>
       </c>
       <c r="O100">
-        <v>0.761139528367347</v>
+        <v>0.7592399733673471</v>
       </c>
       <c r="P100">
-        <v>2.283418585102041</v>
+        <v>2.277719920102041</v>
       </c>
       <c r="Q100">
-        <v>3.453418585102041</v>
+        <v>3.447719920102041</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.097237430472684</v>
+        <v>4.135089182597866</v>
       </c>
       <c r="T100">
-        <v>28.23880840172723</v>
+        <v>56.29060482728409</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.088710188070079</v>
+        <v>5.03730907505927</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0824111418259787</v>
-      </c>
-      <c r="C101">
-        <v>1.198504527769741</v>
-      </c>
-      <c r="D101">
-        <v>12.18110452776974</v>
-      </c>
-      <c r="E101">
-        <v>1.8026</v>
-      </c>
-      <c r="F101">
-        <v>13.6026</v>
-      </c>
-      <c r="G101">
-        <v>2.62</v>
-      </c>
-      <c r="H101">
-        <v>1.94</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.959183673469388</v>
-      </c>
-      <c r="K101">
-        <v>1.17</v>
-      </c>
-      <c r="L101">
-        <v>3.789183673469388</v>
-      </c>
-      <c r="M101">
-        <v>0.7522237800000001</v>
-      </c>
-      <c r="N101">
-        <v>3.036959893469388</v>
-      </c>
-      <c r="O101">
-        <v>0.7592399733673471</v>
-      </c>
-      <c r="P101">
-        <v>2.277719920102041</v>
-      </c>
-      <c r="Q101">
-        <v>3.447719920102041</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.135089182597866</v>
-      </c>
-      <c r="T101">
-        <v>56.29060482728409</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.041475</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.03730907505927</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
